--- a/experiments/results.xlsx
+++ b/experiments/results.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lvuorenk/Documents/vaikkari/paulioptnew/pauliopt/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B03C7ED-2265-1646-9D66-7BCD42C321C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707D1B80-5C91-E24D-8E35-DF7B4D479676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="4" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="line6" sheetId="1" r:id="rId1"/>
-    <sheet name="Molecules" sheetId="11" r:id="rId2"/>
-    <sheet name="quito5" sheetId="5" r:id="rId3"/>
-    <sheet name="grid9" sheetId="6" r:id="rId4"/>
-    <sheet name="guadalupe16" sheetId="7" r:id="rId5"/>
-    <sheet name="grid9-5" sheetId="8" r:id="rId6"/>
-    <sheet name="guadalupe16-8" sheetId="9" r:id="rId7"/>
-    <sheet name="guadalupe16-8legs" sheetId="10" r:id="rId8"/>
+    <sheet name="more gadgets" sheetId="12" r:id="rId2"/>
+    <sheet name="Molecules" sheetId="11" r:id="rId3"/>
+    <sheet name="quito5" sheetId="5" r:id="rId4"/>
+    <sheet name="grid9" sheetId="6" r:id="rId5"/>
+    <sheet name="guadalupe16" sheetId="7" r:id="rId6"/>
+    <sheet name="grid9-5" sheetId="8" r:id="rId7"/>
+    <sheet name="guadalupe16-8" sheetId="9" r:id="rId8"/>
+    <sheet name="guadalupe16-8legs" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="69">
   <si>
     <t>gadgets</t>
   </si>
@@ -921,10 +922,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>line6!$A$2:$A$29</c:f>
+              <c:f>line6!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1008,16 +1009,61 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>line6!$O$2:$O$29</c:f>
+              <c:f>line6!$O$2:$O$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1100,6 +1146,51 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1143,10 +1234,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>line6!$A$2:$A$29</c:f>
+              <c:f>line6!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1230,16 +1321,61 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>line6!$P$2:$P$29</c:f>
+              <c:f>line6!$P$2:$P$44</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.61538461538461542</c:v>
                 </c:pt>
@@ -1323,6 +1459,51 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.98378606022320492</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.98645759087669271</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.99514942888436864</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.98781332225453533</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.98963861511245899</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.99075678798382438</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.99249490725849687</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.99508722678965311</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.99430415796468574</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.9981921721052156</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.99231294841134265</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.9929291287386216</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.99233536680744572</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.99277434893873262</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.99290882778581768</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.99030006978367058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1362,10 +1543,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>line6!$A$2:$A$29</c:f>
+              <c:f>line6!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1449,16 +1630,61 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>line6!$Q$2:$Q$29</c:f>
+              <c:f>line6!$Q$2:$Q$44</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.94082840236686405</c:v>
                 </c:pt>
@@ -1542,6 +1768,51 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.53337544746262378</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.5174625801853171</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.50352057580973242</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.48774407976734518</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.48079353045236289</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.47336799537839397</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.46670955291090382</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.45989572889512731</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.45462312511866332</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.45367441019614935</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.44832593098735907</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.44318920676202855</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.44063819802909432</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.43895830197200064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.43408104196816205</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.43098394975575716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1584,10 +1855,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>line6!$A$2:$A$29</c:f>
+              <c:f>line6!$A$2:$A$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1671,16 +1942,61 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>line6!$R$2:$R$29</c:f>
+              <c:f>line6!$R$2:$R$44</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="43"/>
                 <c:pt idx="0">
                   <c:v>0.53254437869822491</c:v>
                 </c:pt>
@@ -1764,6 +2080,51 @@
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.53253316487681623</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.51728439059158948</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.50336410577374424</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.49203711397313393</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.48193075562294668</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.47325245522819182</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.46510131875201027</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.45819129737317027</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.45671160053161192</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.45231853927506099</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.44815510761872229</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.44253901170351101</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.44001251368684502</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.43956043956043961</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.43531114327062231</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.43049546406140959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13271,16 +13632,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13312,16 +13673,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13441,16 +13802,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13883,7 +14244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BACF18-5131-0846-91EB-6262D6E37819}">
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
@@ -13946,43 +14307,43 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>16.899999999999999</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>5.5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>10.4</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>4.5</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>15.9</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>7.9</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>9</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.3</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>-38.5</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>-5.9</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>-43.4</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>-46.7</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>43.6</v>
       </c>
       <c r="O2">
@@ -14005,43 +14366,43 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>28.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>23.6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>26.6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>11.5</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>20</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>10.1</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>-17.2</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>-6.7</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>-24.8</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>-29.8</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>30.7</v>
       </c>
       <c r="O3">
@@ -14064,43 +14425,43 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>39</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>12.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>34.799999999999997</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>11.8</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>33.5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>15.3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>28.8</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>14.3</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>-10.8</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>-14.1</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>-14</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>-26.2</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>22.4</v>
       </c>
       <c r="O4">
@@ -14123,43 +14484,43 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>46.4</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>17.8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>42.9</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>17</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>38.6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>21.3</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>35.1</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>19.899999999999999</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>-7.5</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-16.8</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>-9.1</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>-24.4</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>19.7</v>
       </c>
       <c r="O5">
@@ -14182,43 +14543,43 @@
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>54.7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>23.3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>52.8</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>22.5</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>45.6</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>27.1</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>41.2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>25.8</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>-3.5</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>-16.600000000000001</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>-9.6</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>-24.7</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>16.3</v>
       </c>
       <c r="O6">
@@ -14241,43 +14602,43 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>63.3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>32.299999999999997</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>58.8</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>32</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>50.9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>40.1</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>47.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>35.700000000000003</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>-7.1</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>-19.600000000000001</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>-6.7</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>-25</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>24.1</v>
       </c>
       <c r="O7">
@@ -14300,43 +14661,43 @@
       <c r="A8">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>68.5</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>27.8</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>66</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>27.4</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>54.8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>32.799999999999997</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>52.1</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>31.5</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>-3.6</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>-20</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>-23.9</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>18</v>
       </c>
       <c r="O8">
@@ -14359,43 +14720,43 @@
       <c r="A9">
         <v>16</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>75.3</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>30.1</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>72.3</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>29.6</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>59.4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>35.200000000000003</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>56.3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>33.700000000000003</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>-4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-21.1</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>-5.2</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>-25.2</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>16.899999999999999</v>
       </c>
       <c r="O9">
@@ -14418,43 +14779,43 @@
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>80.7</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>31.1</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>77.2</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>30.7</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>63</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>37</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>59.6</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>34.6</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>-4.3</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>-21.9</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>-5.4</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>-26.1</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>19</v>
       </c>
       <c r="O10">
@@ -14477,43 +14838,43 @@
       <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>86.9</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>33</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>82.9</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>32.799999999999997</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>66.2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>37.799999999999997</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>64.099999999999994</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>37</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>-23.8</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>-3.2</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>-26.2</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>14.5</v>
       </c>
       <c r="O11">
@@ -14536,43 +14897,43 @@
       <c r="A12">
         <v>22</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>93.9</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>34.200000000000003</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>90.3</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>34</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>70.5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>38.700000000000003</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>67.7</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>37.9</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>-3.8</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>-24.9</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>-4</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>-27.9</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>13.2</v>
       </c>
       <c r="O12">
@@ -14595,43 +14956,43 @@
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>99.2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>35.9</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>96.6</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>35.1</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>74.7</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>40.5</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>71.599999999999994</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>39.700000000000003</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>-2.6</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>-24.7</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>-27.8</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>12.8</v>
       </c>
       <c r="O13">
@@ -14654,43 +15015,43 @@
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>105</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>37.700000000000003</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>100.7</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>37.1</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>76.8</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>42.6</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>75</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>41.1</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>-26.9</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>-28.6</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>13</v>
       </c>
       <c r="O14">
@@ -14713,43 +15074,43 @@
       <c r="A15">
         <v>28</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>108.7</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>104.7</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>39</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>79.2</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>44</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>78.2</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>43</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>-3.7</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>-27.1</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>-1.3</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>-28.1</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>10.6</v>
       </c>
       <c r="O15">
@@ -14772,43 +15133,43 @@
       <c r="A16">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>114.2</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>42.6</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>111.6</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>41.5</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>82.8</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>47.2</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>81.5</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>46.8</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>-27.5</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>-1.6</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>-28.6</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>10.8</v>
       </c>
       <c r="O16">
@@ -14831,43 +15192,43 @@
       <c r="A17">
         <v>32</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>121</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>46.8</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>115.4</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>45.7</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>86.2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>51.3</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>83.8</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>50.7</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>-28.8</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>-2.8</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <v>-30.7</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>9.6</v>
       </c>
       <c r="O17">
@@ -14890,43 +15251,43 @@
       <c r="A18">
         <v>34</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>124.6</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>49.2</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>121</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>48.6</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>88.7</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>54.2</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>85.6</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>52.5</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>-2.9</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>-28.8</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>-3.5</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <v>-31.3</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>10.199999999999999</v>
       </c>
       <c r="O18">
@@ -14949,43 +15310,43 @@
       <c r="A19">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>128.69999999999999</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>53</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>125.2</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>52.1</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>91.4</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>58.5</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>89.5</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>56.9</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>-2.7</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>-29</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>-2.1</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <v>-30.5</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>10.4</v>
       </c>
       <c r="O19">
@@ -15008,43 +15369,43 @@
       <c r="A20">
         <v>38</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>135.30000000000001</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>55</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>132.6</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>54.6</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>94.1</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>59.8</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>93</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>59.7</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>-2</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>-30.5</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>-1.2</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <v>-31.3</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="2">
         <v>8.6999999999999993</v>
       </c>
       <c r="O20">
@@ -15067,43 +15428,43 @@
       <c r="A21">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>138.4</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>57.1</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>135.4</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>56.1</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>96.8</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>62.1</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>94.6</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>61.1</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>-30.1</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <v>-31.6</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>8.8000000000000007</v>
       </c>
       <c r="O21">
@@ -15126,43 +15487,43 @@
       <c r="A22">
         <v>60</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>190.3</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>88.6</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>182.6</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>88.1</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>122.9</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>93.5</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>121.1</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>93.4</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>-4</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>-35.4</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>-1.5</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <v>-36.4</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>5.5</v>
       </c>
       <c r="O22">
@@ -15185,43 +15546,43 @@
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>235.1</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>123.2</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>230.1</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>121.5</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>145.6</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>123.9</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>143.5</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>122.1</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>-2.1</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>-38.1</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>-1.4</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <v>-39</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>0.6</v>
       </c>
       <c r="O23">
@@ -15244,43 +15605,43 @@
       <c r="A24">
         <v>100</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>278.10000000000002</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>160.4</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>274.60000000000002</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>158.30000000000001</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>166.7</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>157.5</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>165.6</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>156.9</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="2">
         <v>-1.3</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>-40.1</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>-0.7</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="2">
         <v>-40.5</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>-1.8</v>
       </c>
       <c r="O24">
@@ -15303,43 +15664,43 @@
       <c r="A25">
         <v>120</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>321.7</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>189.5</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>317.39999999999998</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>185.6</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>186.1</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>177.1</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>185.4</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>177.8</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="2">
         <v>-1.3</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>-42.2</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>-0.4</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="2">
         <v>-42.4</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="2">
         <v>-6.5</v>
       </c>
       <c r="O25">
@@ -15362,43 +15723,43 @@
       <c r="A26">
         <v>140</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>361</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>252.2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>356.9</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>249.1</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>204</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>230.7</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>203.6</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>233</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>-43.5</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>-0.2</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="2">
         <v>-43.6</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>-8.5</v>
       </c>
       <c r="O26">
@@ -15421,43 +15782,43 @@
       <c r="A27">
         <v>160</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>401</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>311</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>394.2</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>305.5</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>221.2</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>276.89999999999998</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>221.8</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>277.2</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="2">
         <v>-1.7</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>-44.8</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>0.3</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="2">
         <v>-44.7</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>-11</v>
       </c>
       <c r="O27">
@@ -15480,43 +15841,43 @@
       <c r="A28">
         <v>180</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>438.5</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>320.10000000000002</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>432</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>313.7</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>237.7</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>279.5</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>237.3</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>276.8</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="2">
         <v>-1.5</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>-45.8</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="2">
         <v>-0.2</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="2">
         <v>-45.9</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>-12.7</v>
       </c>
       <c r="O28">
@@ -15539,43 +15900,43 @@
       <c r="A29">
         <v>200</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>474.9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>360.8</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>467.2</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>356.6</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>253.3</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <v>310.60000000000002</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>252.9</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>311</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="2">
         <v>-1.6</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>-46.7</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="2">
         <v>-0.2</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="2">
         <v>-46.7</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>-13.9</v>
       </c>
       <c r="O29">
@@ -15595,24 +15956,944 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30" s="2">
+        <v>561.20000000000005</v>
+      </c>
+      <c r="C30" s="2">
+        <v>284.8</v>
+      </c>
+      <c r="D30" s="2">
+        <v>553.6</v>
+      </c>
+      <c r="E30" s="2">
+        <v>279.60000000000002</v>
+      </c>
+      <c r="F30" s="2">
+        <v>290.39999999999998</v>
+      </c>
+      <c r="G30" s="2">
+        <v>199.9</v>
+      </c>
+      <c r="H30" s="2">
+        <v>290.3</v>
+      </c>
+      <c r="I30" s="2">
+        <v>200.6</v>
+      </c>
+      <c r="J30" s="2">
+        <v>-1.4</v>
+      </c>
+      <c r="K30" s="2">
+        <v>-48.3</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>-48.3</v>
+      </c>
+      <c r="N30" s="2">
+        <v>-29.8</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" ref="P30:P55" si="3">D30/B30</f>
+        <v>0.98645759087669271</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" ref="Q30:Q55" si="4">F30/B30</f>
+        <v>0.5174625801853171</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" ref="R30:R55" si="5">H30/B30</f>
+        <v>0.51728439059158948</v>
+      </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
+      <c r="A31">
+        <v>300</v>
+      </c>
+      <c r="B31" s="2">
+        <v>639.1</v>
+      </c>
+      <c r="C31" s="2">
+        <v>387</v>
+      </c>
+      <c r="D31" s="2">
+        <v>636</v>
+      </c>
+      <c r="E31" s="2">
+        <v>385.1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>321.8</v>
+      </c>
+      <c r="G31" s="2">
+        <v>259.2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>321.7</v>
+      </c>
+      <c r="I31" s="2">
+        <v>257.8</v>
+      </c>
+      <c r="J31" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="K31" s="2">
+        <v>-49.6</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>-49.7</v>
+      </c>
+      <c r="N31" s="2">
+        <v>-33</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99514942888436864</v>
+      </c>
+      <c r="Q31" s="1">
+        <f t="shared" si="4"/>
+        <v>0.50352057580973242</v>
+      </c>
+      <c r="R31" s="1">
+        <f t="shared" si="5"/>
+        <v>0.50336410577374424</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-    </row>
-    <row r="33" spans="16:18" x14ac:dyDescent="0.2">
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
+      <c r="A32">
+        <v>350</v>
+      </c>
+      <c r="B32" s="2">
+        <v>722.1</v>
+      </c>
+      <c r="C32" s="2">
+        <v>511.9</v>
+      </c>
+      <c r="D32" s="2">
+        <v>713.3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>504.6</v>
+      </c>
+      <c r="F32" s="2">
+        <v>352.2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>323.3</v>
+      </c>
+      <c r="H32" s="2">
+        <v>355.3</v>
+      </c>
+      <c r="I32" s="2">
+        <v>326.10000000000002</v>
+      </c>
+      <c r="J32" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="K32" s="2">
+        <v>-51.2</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M32" s="2">
+        <v>-50.8</v>
+      </c>
+      <c r="N32" s="2">
+        <v>-36.799999999999997</v>
+      </c>
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32" s="1">
+        <f t="shared" si="3"/>
+        <v>0.98781332225453533</v>
+      </c>
+      <c r="Q32" s="1">
+        <f t="shared" si="4"/>
+        <v>0.48774407976734518</v>
+      </c>
+      <c r="R32" s="1">
+        <f t="shared" si="5"/>
+        <v>0.49203711397313393</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>400</v>
+      </c>
+      <c r="B33" s="2">
+        <v>791.4</v>
+      </c>
+      <c r="C33" s="2">
+        <v>722.3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>783.2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>709.2</v>
+      </c>
+      <c r="F33" s="2">
+        <v>380.5</v>
+      </c>
+      <c r="G33" s="2">
+        <v>433.4</v>
+      </c>
+      <c r="H33" s="2">
+        <v>381.4</v>
+      </c>
+      <c r="I33" s="2">
+        <v>432.8</v>
+      </c>
+      <c r="J33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="2">
+        <v>-51.9</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M33" s="2">
+        <v>-51.8</v>
+      </c>
+      <c r="N33" s="2">
+        <v>-40</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1">
+        <f t="shared" si="3"/>
+        <v>0.98963861511245899</v>
+      </c>
+      <c r="Q33" s="1">
+        <f t="shared" si="4"/>
+        <v>0.48079353045236289</v>
+      </c>
+      <c r="R33" s="1">
+        <f t="shared" si="5"/>
+        <v>0.48193075562294668</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>450</v>
+      </c>
+      <c r="B34" s="2">
+        <v>865.5</v>
+      </c>
+      <c r="C34" s="2">
+        <v>888.8</v>
+      </c>
+      <c r="D34" s="2">
+        <v>857.5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>878.4</v>
+      </c>
+      <c r="F34" s="2">
+        <v>409.7</v>
+      </c>
+      <c r="G34" s="2">
+        <v>509.8</v>
+      </c>
+      <c r="H34" s="2">
+        <v>409.6</v>
+      </c>
+      <c r="I34" s="2">
+        <v>510.4</v>
+      </c>
+      <c r="J34" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="K34" s="2">
+        <v>-52.7</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>-52.7</v>
+      </c>
+      <c r="N34" s="2">
+        <v>-42.6</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99075678798382438</v>
+      </c>
+      <c r="Q34" s="1">
+        <f t="shared" si="4"/>
+        <v>0.47336799537839397</v>
+      </c>
+      <c r="R34" s="1">
+        <f t="shared" si="5"/>
+        <v>0.47325245522819182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>500</v>
+      </c>
+      <c r="B35" s="2">
+        <v>932.7</v>
+      </c>
+      <c r="C35" s="2">
+        <v>965.6</v>
+      </c>
+      <c r="D35" s="2">
+        <v>925.7</v>
+      </c>
+      <c r="E35" s="2">
+        <v>955.9</v>
+      </c>
+      <c r="F35" s="2">
+        <v>435.3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>546.20000000000005</v>
+      </c>
+      <c r="H35" s="2">
+        <v>433.8</v>
+      </c>
+      <c r="I35" s="2">
+        <v>541.70000000000005</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K35" s="2">
+        <v>-53.3</v>
+      </c>
+      <c r="L35" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="M35" s="2">
+        <v>-53.5</v>
+      </c>
+      <c r="N35" s="2">
+        <v>-43.4</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99249490725849687</v>
+      </c>
+      <c r="Q35" s="1">
+        <f t="shared" si="4"/>
+        <v>0.46670955291090382</v>
+      </c>
+      <c r="R35" s="1">
+        <f t="shared" si="5"/>
+        <v>0.46510131875201027</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>550</v>
+      </c>
+      <c r="B36" s="2">
+        <v>997.4</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1167</v>
+      </c>
+      <c r="D36" s="2">
+        <v>992.5</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1154.8</v>
+      </c>
+      <c r="F36" s="2">
+        <v>458.7</v>
+      </c>
+      <c r="G36" s="2">
+        <v>628.79999999999995</v>
+      </c>
+      <c r="H36" s="2">
+        <v>457</v>
+      </c>
+      <c r="I36" s="2">
+        <v>630.4</v>
+      </c>
+      <c r="J36" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="K36" s="2">
+        <v>-54</v>
+      </c>
+      <c r="L36" s="2">
+        <v>-0.4</v>
+      </c>
+      <c r="M36" s="2">
+        <v>-54.2</v>
+      </c>
+      <c r="N36" s="2">
+        <v>-46.1</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99508722678965311</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="4"/>
+        <v>0.45989572889512731</v>
+      </c>
+      <c r="R36" s="1">
+        <f t="shared" si="5"/>
+        <v>0.45819129737317027</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>600</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1053.4000000000001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1261.4000000000001</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1047.4000000000001</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1252.0999999999999</v>
+      </c>
+      <c r="F37" s="2">
+        <v>478.9</v>
+      </c>
+      <c r="G37" s="2">
+        <v>668.5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>481.1</v>
+      </c>
+      <c r="I37" s="2">
+        <v>671</v>
+      </c>
+      <c r="J37" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="K37" s="2">
+        <v>-54.5</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="2">
+        <v>-54.3</v>
+      </c>
+      <c r="N37" s="2">
+        <v>-47</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99430415796468574</v>
+      </c>
+      <c r="Q37" s="1">
+        <f t="shared" si="4"/>
+        <v>0.45462312511866332</v>
+      </c>
+      <c r="R37" s="1">
+        <f t="shared" si="5"/>
+        <v>0.45671160053161192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>650</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1106.3</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1437.1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1104.3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1429.9</v>
+      </c>
+      <c r="F38" s="2">
+        <v>501.9</v>
+      </c>
+      <c r="G38" s="2">
+        <v>747.7</v>
+      </c>
+      <c r="H38" s="2">
+        <v>500.4</v>
+      </c>
+      <c r="I38" s="2">
+        <v>741.8</v>
+      </c>
+      <c r="J38" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="K38" s="2">
+        <v>-54.6</v>
+      </c>
+      <c r="L38" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="M38" s="2">
+        <v>-54.8</v>
+      </c>
+      <c r="N38" s="2">
+        <v>-48</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38" s="1">
+        <f t="shared" si="3"/>
+        <v>0.9981921721052156</v>
+      </c>
+      <c r="Q38" s="1">
+        <f t="shared" si="4"/>
+        <v>0.45367441019614935</v>
+      </c>
+      <c r="R38" s="1">
+        <f t="shared" si="5"/>
+        <v>0.45231853927506099</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>700</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1170.8</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1646.5</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1161.8</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1633.2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>524.9</v>
+      </c>
+      <c r="G39" s="2">
+        <v>830.9</v>
+      </c>
+      <c r="H39" s="2">
+        <v>524.70000000000005</v>
+      </c>
+      <c r="I39" s="2">
+        <v>830.9</v>
+      </c>
+      <c r="J39" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K39" s="2">
+        <v>-55.2</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>-55.2</v>
+      </c>
+      <c r="N39" s="2">
+        <v>-49.5</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99231294841134265</v>
+      </c>
+      <c r="Q39" s="1">
+        <f t="shared" si="4"/>
+        <v>0.44832593098735907</v>
+      </c>
+      <c r="R39" s="1">
+        <f t="shared" si="5"/>
+        <v>0.44815510761872229</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>750</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1230.4000000000001</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1885.2</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1221.7</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1875.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>545.29999999999995</v>
+      </c>
+      <c r="G40" s="2">
+        <v>927.8</v>
+      </c>
+      <c r="H40" s="2">
+        <v>544.5</v>
+      </c>
+      <c r="I40" s="2">
+        <v>928.9</v>
+      </c>
+      <c r="J40" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K40" s="2">
+        <v>-55.7</v>
+      </c>
+      <c r="L40" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M40" s="2">
+        <v>-55.7</v>
+      </c>
+      <c r="N40" s="2">
+        <v>-50.8</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40" s="1">
+        <f t="shared" si="3"/>
+        <v>0.9929291287386216</v>
+      </c>
+      <c r="Q40" s="1">
+        <f t="shared" si="4"/>
+        <v>0.44318920676202855</v>
+      </c>
+      <c r="R40" s="1">
+        <f t="shared" si="5"/>
+        <v>0.44253901170351101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>800</v>
+      </c>
+      <c r="B41" s="2">
+        <v>1278.5999999999999</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2073.1999999999998</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1268.8</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2057.5</v>
+      </c>
+      <c r="F41" s="2">
+        <v>563.4</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1000.1</v>
+      </c>
+      <c r="H41" s="2">
+        <v>562.6</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1001.8</v>
+      </c>
+      <c r="J41" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K41" s="2">
+        <v>-55.9</v>
+      </c>
+      <c r="L41" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M41" s="2">
+        <v>-56</v>
+      </c>
+      <c r="N41" s="2">
+        <v>-51.8</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99233536680744572</v>
+      </c>
+      <c r="Q41" s="1">
+        <f t="shared" si="4"/>
+        <v>0.44063819802909432</v>
+      </c>
+      <c r="R41" s="1">
+        <f t="shared" si="5"/>
+        <v>0.44001251368684502</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>850</v>
+      </c>
+      <c r="B42" s="2">
+        <v>1328.6</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2291.9</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1319</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2264.1999999999998</v>
+      </c>
+      <c r="F42" s="2">
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1081.8</v>
+      </c>
+      <c r="H42" s="2">
+        <v>584</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1082.9000000000001</v>
+      </c>
+      <c r="J42" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K42" s="2">
+        <v>-56.1</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="M42" s="2">
+        <v>-56</v>
+      </c>
+      <c r="N42" s="2">
+        <v>-52.8</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99277434893873262</v>
+      </c>
+      <c r="Q42" s="1">
+        <f t="shared" si="4"/>
+        <v>0.43895830197200064</v>
+      </c>
+      <c r="R42" s="1">
+        <f t="shared" si="5"/>
+        <v>0.43956043956043961</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>900</v>
+      </c>
+      <c r="B43" s="2">
+        <v>1382</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2515.6999999999998</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1372.2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2495.6999999999998</v>
+      </c>
+      <c r="F43" s="2">
+        <v>599.9</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1158</v>
+      </c>
+      <c r="H43" s="2">
+        <v>601.6</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1165.4000000000001</v>
+      </c>
+      <c r="J43" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K43" s="2">
+        <v>-56.6</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="M43" s="2">
+        <v>-56.5</v>
+      </c>
+      <c r="N43" s="2">
+        <v>-54</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99290882778581768</v>
+      </c>
+      <c r="Q43" s="1">
+        <f t="shared" si="4"/>
+        <v>0.43408104196816205</v>
+      </c>
+      <c r="R43" s="1">
+        <f t="shared" si="5"/>
+        <v>0.43531114327062231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>950</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1433</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2741.1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1419.1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2715.7</v>
+      </c>
+      <c r="F44" s="2">
+        <v>617.6</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1238.5</v>
+      </c>
+      <c r="H44" s="2">
+        <v>616.9</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1235.2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K44" s="2">
+        <v>-56.9</v>
+      </c>
+      <c r="L44" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M44" s="2">
+        <v>-57</v>
+      </c>
+      <c r="N44" s="2">
+        <v>-54.8</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44" s="1">
+        <f t="shared" si="3"/>
+        <v>0.99030006978367058</v>
+      </c>
+      <c r="Q44" s="1">
+        <f t="shared" si="4"/>
+        <v>0.43098394975575716</v>
+      </c>
+      <c r="R44" s="1">
+        <f t="shared" si="5"/>
+        <v>0.43049546406140959</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="16:18" x14ac:dyDescent="0.2">
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15621,6 +16902,764 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF14EA2-C2BC-8F46-9AC9-3F9525E5AB66}">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>200</v>
+      </c>
+      <c r="B2" s="2">
+        <v>474.6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>194.2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>468.7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>192.8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>254.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="H2" s="2">
+        <v>253.8</v>
+      </c>
+      <c r="I2" s="2">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-46.4</v>
+      </c>
+      <c r="L2" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="M2" s="2">
+        <v>-46.5</v>
+      </c>
+      <c r="N2" s="2">
+        <v>-24.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>250</v>
+      </c>
+      <c r="B3" s="2">
+        <v>561.20000000000005</v>
+      </c>
+      <c r="C3" s="2">
+        <v>284.8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>553.6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>279.60000000000002</v>
+      </c>
+      <c r="F3" s="2">
+        <v>290.39999999999998</v>
+      </c>
+      <c r="G3" s="2">
+        <v>199.9</v>
+      </c>
+      <c r="H3" s="2">
+        <v>290.3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>200.6</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-1.4</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-48.3</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-48.3</v>
+      </c>
+      <c r="N3" s="2">
+        <v>-29.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" s="2">
+        <v>639.1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>387</v>
+      </c>
+      <c r="D4" s="2">
+        <v>636</v>
+      </c>
+      <c r="E4" s="2">
+        <v>385.1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>321.8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>259.2</v>
+      </c>
+      <c r="H4" s="2">
+        <v>321.7</v>
+      </c>
+      <c r="I4" s="2">
+        <v>257.8</v>
+      </c>
+      <c r="J4" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>-49.6</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>-49.7</v>
+      </c>
+      <c r="N4" s="2">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>350</v>
+      </c>
+      <c r="B5" s="2">
+        <v>722.1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>511.9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>713.3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>504.6</v>
+      </c>
+      <c r="F5" s="2">
+        <v>352.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>323.3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>355.3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>326.10000000000002</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>-51.2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M5" s="2">
+        <v>-50.8</v>
+      </c>
+      <c r="N5" s="2">
+        <v>-36.799999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>400</v>
+      </c>
+      <c r="B6" s="2">
+        <v>791.4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>722.3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>783.2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>709.2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>380.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>433.4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>381.4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>432.8</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>-51.9</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M6" s="2">
+        <v>-51.8</v>
+      </c>
+      <c r="N6" s="2">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>450</v>
+      </c>
+      <c r="B7" s="2">
+        <v>865.5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>888.8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>857.5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>878.4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>409.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>509.8</v>
+      </c>
+      <c r="H7" s="2">
+        <v>409.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>510.4</v>
+      </c>
+      <c r="J7" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="K7" s="2">
+        <v>-52.7</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>-52.7</v>
+      </c>
+      <c r="N7" s="2">
+        <v>-42.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>500</v>
+      </c>
+      <c r="B8" s="2">
+        <v>932.7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>965.6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>925.7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>955.9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>435.3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>546.20000000000005</v>
+      </c>
+      <c r="H8" s="2">
+        <v>433.8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>541.70000000000005</v>
+      </c>
+      <c r="J8" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K8" s="2">
+        <v>-53.3</v>
+      </c>
+      <c r="L8" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="M8" s="2">
+        <v>-53.5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>-43.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>550</v>
+      </c>
+      <c r="B9" s="2">
+        <v>997.4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1167</v>
+      </c>
+      <c r="D9" s="2">
+        <v>992.5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1154.8</v>
+      </c>
+      <c r="F9" s="2">
+        <v>458.7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>628.79999999999995</v>
+      </c>
+      <c r="H9" s="2">
+        <v>457</v>
+      </c>
+      <c r="I9" s="2">
+        <v>630.4</v>
+      </c>
+      <c r="J9" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="K9" s="2">
+        <v>-54</v>
+      </c>
+      <c r="L9" s="2">
+        <v>-0.4</v>
+      </c>
+      <c r="M9" s="2">
+        <v>-54.2</v>
+      </c>
+      <c r="N9" s="2">
+        <v>-46.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>600</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1053.4000000000001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1261.4000000000001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1047.4000000000001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1252.0999999999999</v>
+      </c>
+      <c r="F10" s="2">
+        <v>478.9</v>
+      </c>
+      <c r="G10" s="2">
+        <v>668.5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>481.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>671</v>
+      </c>
+      <c r="J10" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="K10" s="2">
+        <v>-54.5</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="2">
+        <v>-54.3</v>
+      </c>
+      <c r="N10" s="2">
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>650</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1106.3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1437.1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1104.3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1429.9</v>
+      </c>
+      <c r="F11" s="2">
+        <v>501.9</v>
+      </c>
+      <c r="G11" s="2">
+        <v>747.7</v>
+      </c>
+      <c r="H11" s="2">
+        <v>500.4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>741.8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>-54.6</v>
+      </c>
+      <c r="L11" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="M11" s="2">
+        <v>-54.8</v>
+      </c>
+      <c r="N11" s="2">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>700</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1170.8</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1646.5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1161.8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1633.2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>524.9</v>
+      </c>
+      <c r="G12" s="2">
+        <v>830.9</v>
+      </c>
+      <c r="H12" s="2">
+        <v>524.70000000000005</v>
+      </c>
+      <c r="I12" s="2">
+        <v>830.9</v>
+      </c>
+      <c r="J12" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K12" s="2">
+        <v>-55.2</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>-55.2</v>
+      </c>
+      <c r="N12" s="2">
+        <v>-49.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>750</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1230.4000000000001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1885.2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1221.7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1875.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>545.29999999999995</v>
+      </c>
+      <c r="G13" s="2">
+        <v>927.8</v>
+      </c>
+      <c r="H13" s="2">
+        <v>544.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>928.9</v>
+      </c>
+      <c r="J13" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K13" s="2">
+        <v>-55.7</v>
+      </c>
+      <c r="L13" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>-55.7</v>
+      </c>
+      <c r="N13" s="2">
+        <v>-50.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>800</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1278.5999999999999</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2073.1999999999998</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1268.8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2057.5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>563.4</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1000.1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>562.6</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1001.8</v>
+      </c>
+      <c r="J14" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="K14" s="2">
+        <v>-55.9</v>
+      </c>
+      <c r="L14" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M14" s="2">
+        <v>-56</v>
+      </c>
+      <c r="N14" s="2">
+        <v>-51.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>850</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1328.6</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2291.9</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1319</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2264.1999999999998</v>
+      </c>
+      <c r="F15" s="2">
+        <v>583.20000000000005</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1081.8</v>
+      </c>
+      <c r="H15" s="2">
+        <v>584</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1082.9000000000001</v>
+      </c>
+      <c r="J15" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K15" s="2">
+        <v>-56.1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="M15" s="2">
+        <v>-56</v>
+      </c>
+      <c r="N15" s="2">
+        <v>-52.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>900</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1382</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2515.6999999999998</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1372.2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2495.6999999999998</v>
+      </c>
+      <c r="F16" s="2">
+        <v>599.9</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1158</v>
+      </c>
+      <c r="H16" s="2">
+        <v>601.6</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1165.4000000000001</v>
+      </c>
+      <c r="J16" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="K16" s="2">
+        <v>-56.6</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="M16" s="2">
+        <v>-56.5</v>
+      </c>
+      <c r="N16" s="2">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>950</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1433</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2741.1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1419.1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2715.7</v>
+      </c>
+      <c r="F17" s="2">
+        <v>617.6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1238.5</v>
+      </c>
+      <c r="H17" s="2">
+        <v>616.9</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1235.2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K17" s="2">
+        <v>-56.9</v>
+      </c>
+      <c r="L17" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="M17" s="2">
+        <v>-57</v>
+      </c>
+      <c r="N17" s="2">
+        <v>-54.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53CADA0-3FD9-B748-A167-0AF6A36FD04E}">
   <dimension ref="C3:L44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -16859,7 +18898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F460-F86E-7C4A-B7F3-1237ED3448DF}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -16924,43 +18963,43 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>0.6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>7.5</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>0.6</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>9.6</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>6.7</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>-22.7</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>-1</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>-30.2</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>-30.9</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>266.7</v>
       </c>
       <c r="O2">
@@ -16983,43 +19022,43 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>16.3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>15</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>14.9</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>2.7</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>13.1</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>2.6</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>-8</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>-8.6</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>-12.1</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>-19.600000000000001</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>170</v>
       </c>
       <c r="O3">
@@ -17042,43 +19081,43 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>23.8</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>21.4</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>1.4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>19.899999999999999</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>3.2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>18.100000000000001</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>-10.1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>-16.399999999999999</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>-9</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>-23.9</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>113.3</v>
       </c>
       <c r="O4">
@@ -17101,43 +19140,43 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>29.4</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>1.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>1.9</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>24.4</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>3.7</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>22.8</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>3.8</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>-4.8</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-17</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>-6.6</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>-22.4</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>94.7</v>
       </c>
       <c r="O5">
@@ -17160,43 +19199,43 @@
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>34.9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>33.799999999999997</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>28</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>26.2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>-3.2</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>-19.8</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>-6.4</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>-24.9</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>78.3</v>
       </c>
       <c r="O6">
@@ -17219,43 +19258,43 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>38.9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>2.7</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>37.9</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>2.6</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>30.8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>4.8</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>29.3</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>4.5</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>-2.6</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>-20.8</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>-24.7</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>77.8</v>
       </c>
       <c r="O7">
@@ -17278,43 +19317,43 @@
       <c r="A8">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>43.2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>3.1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>42.2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>32.9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>32</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>5.2</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>-23.8</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>-2.7</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>-25.9</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>64.5</v>
       </c>
       <c r="O8">
@@ -17337,43 +19376,43 @@
       <c r="A9">
         <v>16</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>46.1</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>3.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>44.9</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>3.6</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>35.4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>5.8</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>35</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>5.5</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>-2.6</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-23.2</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>-24.1</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>65.7</v>
       </c>
       <c r="O9">
@@ -17396,43 +19435,43 @@
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>49.9</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>4</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>48.6</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>4</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>38</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>6.1</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>37</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>6.1</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>-2.6</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>-23.8</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>-2.6</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>-25.9</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>52.5</v>
       </c>
       <c r="O10">
@@ -17455,43 +19494,43 @@
       <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>53.3</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>51.9</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>4.3</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>6.6</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>39.200000000000003</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.4</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>-2.6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>-25.3</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>-1.5</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>-26.5</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>43.5</v>
       </c>
       <c r="O11">
@@ -17514,43 +19553,43 @@
       <c r="A12">
         <v>22</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>56.7</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>4.7</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>55.7</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>42.5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>7</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>41.4</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.7</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>-1.8</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>-25</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>-2.6</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>-27</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>48.9</v>
       </c>
       <c r="O12">
@@ -17573,43 +19612,43 @@
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>59.7</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>5.4</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>58.4</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>5</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>43.5</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>7.5</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>43.1</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>7.2</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>-27.1</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>-0.9</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>-27.8</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>38.9</v>
       </c>
       <c r="O13">
@@ -17632,43 +19671,43 @@
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>63.5</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>5.8</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>61.8</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>5.6</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>45.9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>8.1</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>45.2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>-2.7</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>-27.7</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>-1.5</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>-28.8</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>39.700000000000003</v>
       </c>
       <c r="O14">
@@ -17691,43 +19730,43 @@
       <c r="A15">
         <v>28</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>66.5</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>6.3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>65.7</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>6.3</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>47.5</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>47.1</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>8.3000000000000007</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>-1.2</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>-28.6</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>-0.8</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>-29.2</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>38.1</v>
       </c>
       <c r="O15">
@@ -17750,43 +19789,43 @@
       <c r="A16">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>70.900000000000006</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>7.3</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>68.3</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>7</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>49.8</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>9.6</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>49</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.1</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>-3.7</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>-29.8</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>-1.6</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>-30.9</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>31.5</v>
       </c>
       <c r="O16">
@@ -17809,43 +19848,43 @@
       <c r="A17">
         <v>32</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>72.5</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>7.4</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>71.8</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>7.2</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>51.4</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>50.4</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>9.6</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>-1</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>-29.1</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>-1.9</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <v>-30.5</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>31.1</v>
       </c>
       <c r="O17">
@@ -17868,43 +19907,43 @@
       <c r="A18">
         <v>34</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>75.8</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>7.9</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>74.3</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>7.8</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>53.1</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>10.3</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>51.9</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>10.1</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>-2</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>-29.9</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <v>-31.5</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>30.4</v>
       </c>
       <c r="O18">
@@ -17927,43 +19966,43 @@
       <c r="A19">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>78.599999999999994</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>8.5</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>76.5</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>54.3</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>11</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>53.6</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>10.7</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>-2.7</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>-30.9</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>-1.3</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <v>-31.8</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>29.4</v>
       </c>
       <c r="O19">
@@ -17986,43 +20025,43 @@
       <c r="A20">
         <v>38</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>81.900000000000006</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>81.099999999999994</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>56.3</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>11.5</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>55.8</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>11</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>-1</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>-31.3</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>-0.9</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <v>-31.9</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="2">
         <v>25</v>
       </c>
       <c r="O20">
@@ -18045,43 +20084,43 @@
       <c r="A21">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>85</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>9.5</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>83.7</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>58.4</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>11.8</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>57.2</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>12</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>-1.5</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>-31.3</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>-2.1</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <v>-32.700000000000003</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>24.2</v>
       </c>
       <c r="O21">
@@ -18104,43 +20143,43 @@
       <c r="A22">
         <v>60</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>114</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>16.399999999999999</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>110.8</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>15.9</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>72.599999999999994</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>18.399999999999999</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>72</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>18</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>-2.8</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>-36.299999999999997</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>-0.8</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <v>-36.799999999999997</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>12.2</v>
       </c>
       <c r="O22">
@@ -18163,43 +20202,43 @@
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>137</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>24.1</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>136.5</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>23.6</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>84.8</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>24.4</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>84.5</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>24.6</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>-0.4</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>-38.1</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>-0.4</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <v>-38.299999999999997</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>1.2</v>
       </c>
       <c r="O23">
@@ -18222,43 +20261,43 @@
       <c r="A24">
         <v>100</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>160.5</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>33.6</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>158.69999999999999</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>32.5</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>97.2</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>32.200000000000003</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>95.3</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>31.7</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>-39.4</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>-2</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="2">
         <v>-40.6</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>-4.2</v>
       </c>
       <c r="O24">
@@ -18281,43 +20320,43 @@
       <c r="A25">
         <v>120</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>183.9</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>43.3</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>183.5</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>43.6</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>107.2</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>40</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>107.2</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>40</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="2">
         <v>-0.2</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>-41.7</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>0</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="2">
         <v>-41.7</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="2">
         <v>-7.6</v>
       </c>
       <c r="O25">
@@ -18340,43 +20379,43 @@
       <c r="A26">
         <v>140</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>202.4</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>53.2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>202.1</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>53</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>116.4</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>47.7</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>115.5</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>47.5</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="2">
         <v>-0.1</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>-42.5</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>-0.8</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="2">
         <v>-42.9</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>-10.3</v>
       </c>
       <c r="O26">
@@ -18399,43 +20438,43 @@
       <c r="A27">
         <v>160</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>222.6</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>65.099999999999994</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>221</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>64.599999999999994</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>124.7</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>55.7</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>123.8</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>54.8</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="2">
         <v>-0.7</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>-44</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>-0.7</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="2">
         <v>-44.4</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>-14.4</v>
       </c>
       <c r="O27">
@@ -18458,43 +20497,43 @@
       <c r="A28">
         <v>180</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>240.9</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>77.599999999999994</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>241</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>76.900000000000006</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>132.80000000000001</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>62.9</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>132.9</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>64</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="2">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>-44.9</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="2">
         <v>0.1</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="2">
         <v>-44.8</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>-18.899999999999999</v>
       </c>
       <c r="O28">
@@ -18517,43 +20556,43 @@
       <c r="A29">
         <v>200</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>258</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>89.4</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>258.5</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>89.6</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>141.5</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <v>72.8</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>140.1</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>72.3</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="2">
         <v>0.2</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>-45.2</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="2">
         <v>-1</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="2">
         <v>-45.7</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>-18.600000000000001</v>
       </c>
       <c r="O29">
@@ -18598,7 +20637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032F0823-5CD8-3940-ADAD-49121E744578}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -18663,43 +20702,43 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>22.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>2.9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>16.399999999999999</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>2.7</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>24.6</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>4</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>14.6</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>3.6</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>-27.1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>9.3000000000000007</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>-40.700000000000003</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>-35.1</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>37.9</v>
       </c>
       <c r="O2">
@@ -18722,43 +20761,43 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>49.8</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>4.2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>44</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>48.6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>5.5</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>36.299999999999997</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>-11.6</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>-2.4</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>-25.3</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>-27.1</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>31</v>
       </c>
       <c r="O3">
@@ -18781,43 +20820,43 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>73.900000000000006</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>5.7</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>68.099999999999994</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>5.6</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>67.2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>6.6</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>57.7</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.1</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>-7.8</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>-9.1</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>-14.1</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>-21.9</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>15.8</v>
       </c>
       <c r="O4">
@@ -18840,43 +20879,43 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>92.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>7.4</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>88.3</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>7.1</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>82</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>8</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>76</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.6</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>-4.2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-11.1</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>-7.3</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>-17.600000000000001</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>8.1</v>
       </c>
       <c r="O5">
@@ -18899,43 +20938,43 @@
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>106.5</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>8.6</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>103.9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>8.4</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>97.1</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>9.5</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>88.8</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>-2.4</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>-8.8000000000000007</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>-8.5</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>-16.600000000000001</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>10.5</v>
       </c>
       <c r="O6">
@@ -18958,43 +20997,43 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>121.8</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>116</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>9.9</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>107.7</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>11</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>101.8</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>10.1</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>-4.8</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>-11.6</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>-5.5</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>-16.399999999999999</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>10</v>
       </c>
       <c r="O7">
@@ -19017,43 +21056,43 @@
       <c r="A8">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>134.19999999999999</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>11.4</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>128</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>11.4</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>118.2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>12.1</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>112.2</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>11.6</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>-11.9</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>-5.0999999999999996</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>-16.399999999999999</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>6.1</v>
       </c>
       <c r="O8">
@@ -19076,43 +21115,43 @@
       <c r="A9">
         <v>16</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>145.80000000000001</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>13.2</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>140.1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>13</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>126.8</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>13.8</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>121.6</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>13</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>-3.9</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-13</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>-16.600000000000001</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>4.5</v>
       </c>
       <c r="O9">
@@ -19135,43 +21174,43 @@
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>155</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>14.6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>147.80000000000001</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>14.2</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>134.19999999999999</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>15.1</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>128.30000000000001</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>14.3</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>-13.4</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>-17.2</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>3.4</v>
       </c>
       <c r="O10">
@@ -19194,43 +21233,43 @@
       <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>164.8</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>160.19999999999999</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>15.7</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>142.6</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>16.7</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>135.6</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>15.9</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>-2.8</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>-13.5</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>-17.7</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>3.7</v>
       </c>
       <c r="O11">
@@ -19253,43 +21292,43 @@
       <c r="A12">
         <v>22</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>175.9</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>17.7</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>170</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>17.399999999999999</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>151.6</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>18.8</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>145.5</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>17.7</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>-3.4</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>-13.8</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>-4</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>-17.3</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>6.2</v>
       </c>
       <c r="O12">
@@ -19312,43 +21351,43 @@
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>186.1</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>19.7</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>180.7</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>19.3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>158.9</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>20.100000000000001</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>152.6</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>19.100000000000001</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>-2.9</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>-14.6</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>-4</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>-18</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>2</v>
       </c>
       <c r="O13">
@@ -19371,43 +21410,43 @@
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>194.5</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>21.5</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>187.8</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>21.1</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>165.9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>21.8</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>159</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>20.6</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>-3.4</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>-14.7</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>-4.2</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>-18.3</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>1.4</v>
       </c>
       <c r="O14">
@@ -19430,43 +21469,43 @@
       <c r="A15">
         <v>28</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>204.6</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>23.2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>199.1</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>23.1</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>173</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>24</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>166.1</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>22.7</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>-2.7</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>-15.4</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>-4</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>-18.8</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>3.4</v>
       </c>
       <c r="O15">
@@ -19489,43 +21528,43 @@
       <c r="A16">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>215.3</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>25.7</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>208.8</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>25.2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>181.1</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>26.1</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>176</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>24.8</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>-3</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>-15.9</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>-2.8</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>-18.3</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>1.6</v>
       </c>
       <c r="O16">
@@ -19548,43 +21587,43 @@
       <c r="A17">
         <v>32</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>225.9</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>28</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>217.8</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>27.7</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>187.8</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>27.8</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>181.1</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>26.6</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>-3.6</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>-16.899999999999999</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>-3.6</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <v>-19.8</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>-0.7</v>
       </c>
       <c r="O17">
@@ -19607,43 +21646,43 @@
       <c r="A18">
         <v>34</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>236.6</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>30.2</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>228.4</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>29.5</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>194.6</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>30.7</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>187.9</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>29.1</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>-3.5</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>-17.8</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>-3.4</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <v>-20.6</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>1.7</v>
       </c>
       <c r="O18">
@@ -19666,43 +21705,43 @@
       <c r="A19">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>245.5</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>32.299999999999997</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>237.7</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>32</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>201.8</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>32.700000000000003</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>195.1</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>31.2</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>-3.2</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>-17.8</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>-3.3</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <v>-20.5</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>1.2</v>
       </c>
       <c r="O19">
@@ -19725,43 +21764,43 @@
       <c r="A20">
         <v>38</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>253.2</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>34.6</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>247.3</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>34.200000000000003</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>208.7</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>34.799999999999997</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>201.5</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>33.4</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>-17.600000000000001</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>-3.4</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <v>-20.399999999999999</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="2">
         <v>0.6</v>
       </c>
       <c r="O20">
@@ -19784,43 +21823,43 @@
       <c r="A21">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>263.8</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>37.200000000000003</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>257.5</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>36.9</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>215.6</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>37.4</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>209.9</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>35.9</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>-2.4</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>-18.3</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>-2.6</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <v>-20.399999999999999</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>0.5</v>
       </c>
       <c r="O21">
@@ -19843,43 +21882,43 @@
       <c r="A22">
         <v>60</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>359.7</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>66.5</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>348.4</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>65.599999999999994</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>280.89999999999998</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>65.099999999999994</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>273</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>62.2</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>-3.1</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>-21.9</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>-2.8</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <v>-24.1</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>-2.1</v>
       </c>
       <c r="O22">
@@ -19902,43 +21941,43 @@
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>450.1</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>105.5</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>438.8</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>104.2</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>342.6</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>98.6</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>336.2</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>96.9</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>-2.5</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>-23.9</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>-1.9</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <v>-25.3</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>-6.5</v>
       </c>
       <c r="O23">
@@ -19961,43 +22000,43 @@
       <c r="A24">
         <v>100</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>544.79999999999995</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>153</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>525.4</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>149.4</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>402.2</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>139.1</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>393.4</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>136.4</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="2">
         <v>-3.6</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>-26.2</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="2">
         <v>-27.8</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>-9.1</v>
       </c>
       <c r="O24">
@@ -20020,43 +22059,43 @@
       <c r="A25">
         <v>120</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>632.4</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>209.6</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>617.29999999999995</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>205.9</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>458.2</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>187.6</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>452.9</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>184.7</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="2">
         <v>-2.4</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>-27.5</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>-1.2</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="2">
         <v>-28.4</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="2">
         <v>-10.5</v>
       </c>
       <c r="O25">
@@ -20079,43 +22118,43 @@
       <c r="A26">
         <v>140</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>716</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>276.2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>702.3</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>270.7</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>510.6</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>238.6</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>506.4</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>233.7</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="2">
         <v>-1.9</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>-28.7</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>-0.8</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="2">
         <v>-29.3</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>-13.6</v>
       </c>
       <c r="O26">
@@ -20138,43 +22177,43 @@
       <c r="A27">
         <v>160</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>806.5</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>351.7</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>788</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>345.5</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>563.9</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>296.60000000000002</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>558.29999999999995</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>292.5</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>-30.1</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>-1</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="2">
         <v>-30.8</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>-15.7</v>
       </c>
       <c r="O27">
@@ -20197,43 +22236,43 @@
       <c r="A28">
         <v>180</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>902.1</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>441.6</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>880.4</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>433</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>616.9</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>362.6</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>610.20000000000005</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>358.2</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="2">
         <v>-2.4</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>-31.6</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="2">
         <v>-32.4</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>-17.899999999999999</v>
       </c>
       <c r="O28">
@@ -20256,43 +22295,43 @@
       <c r="A29">
         <v>200</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>981.5</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>531.1</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>960.9</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>522.70000000000005</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>665.7</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <v>428</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>660</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>422.8</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="2">
         <v>-2.1</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>-32.200000000000003</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="2">
         <v>-0.9</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="2">
         <v>-32.799999999999997</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>-19.399999999999999</v>
       </c>
       <c r="O29">
@@ -20337,7 +22376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180C0165-7B09-2442-A9D2-BF39681A36D2}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -20402,43 +22441,43 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>74.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>10.3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>54.9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>10.5</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>89.4</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>9.5</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>54.7</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>-26.3</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>20</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>-38.799999999999997</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>-26.6</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>-7.8</v>
       </c>
       <c r="O2">
@@ -20461,43 +22500,43 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>146.80000000000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>14.9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>133.6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>15.3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>160.19999999999999</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>12.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>118.4</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>12.1</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>-9</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>9.1</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>-26.1</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>-19.3</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>-13.4</v>
       </c>
       <c r="O3">
@@ -20520,43 +22559,43 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>223.6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>207.7</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>20.3</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>225.6</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>16.5</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>190.6</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>-7.1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>0.9</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>-15.5</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>-14.8</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>-19.100000000000001</v>
       </c>
       <c r="O4">
@@ -20579,43 +22618,43 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>292.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>25.8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>273</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>25</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>276.3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>20.2</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>246.7</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>19.3</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>-6.6</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>-5.4</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>-10.7</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>-15.6</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>-21.7</v>
       </c>
       <c r="O5">
@@ -20638,43 +22677,43 @@
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>341.7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>31.5</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>325.7</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>31.2</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>324.89999999999998</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>23.8</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>295.2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>23.1</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>-4.7</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>-9.1</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>-13.6</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>-24.4</v>
       </c>
       <c r="O6">
@@ -20697,43 +22736,43 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>384.4</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>36.9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>372</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>36.700000000000003</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>365.1</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>28.3</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>341.6</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>27.4</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>-3.2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>-5</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>-6.4</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>-11.1</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>-23.3</v>
       </c>
       <c r="O7">
@@ -20756,43 +22795,43 @@
       <c r="A8">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>414.9</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>41.7</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>401.2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>41.3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>390.5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>32.200000000000003</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>367.6</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>30.8</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>-3.3</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>-5.9</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>-5.9</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>-11.4</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>-22.8</v>
       </c>
       <c r="O8">
@@ -20815,43 +22854,43 @@
       <c r="A9">
         <v>16</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>447.1</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>47</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>438</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>47.8</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>420.7</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>36.700000000000003</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>400.3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>34.799999999999997</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>-2</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>-5.9</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>-4.8</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>-10.5</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>-21.9</v>
       </c>
       <c r="O9">
@@ -20874,43 +22913,43 @@
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>475.9</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>53.4</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>466.4</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>53.3</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>447</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>41.1</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>431</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>39.4</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>-2</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>-6.1</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>-3.6</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>-9.4</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>-23</v>
       </c>
       <c r="O10">
@@ -20933,43 +22972,43 @@
       <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>508.8</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>60.4</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>494.7</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>58.8</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>474.2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>46.6</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>457.1</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>44.4</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>-2.8</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>-6.8</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>-3.6</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>-10.199999999999999</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>-22.8</v>
       </c>
       <c r="O11">
@@ -20992,43 +23031,43 @@
       <c r="A12">
         <v>22</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>530.70000000000005</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>65.099999999999994</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>522.29999999999995</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>65</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>495</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>51.4</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>480.2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>49.5</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>-1.6</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>-6.7</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>-3</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>-9.5</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>-21</v>
       </c>
       <c r="O12">
@@ -21051,43 +23090,43 @@
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>561.1</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>72.099999999999994</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>552</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>72.3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>517.1</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>57.2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>504.6</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>54.6</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>-1.6</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>-7.8</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>-2.4</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>-10.1</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>-20.7</v>
       </c>
       <c r="O13">
@@ -21110,43 +23149,43 @@
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>587.20000000000005</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>79.099999999999994</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>574.29999999999995</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>78.400000000000006</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>534.5</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>61.7</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>523.6</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>59.6</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>-9</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>-2</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>-10.8</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>-22</v>
       </c>
       <c r="O14">
@@ -21169,43 +23208,43 @@
       <c r="A15">
         <v>28</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>611.5</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>86.7</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>602.4</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>85.1</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>556.4</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>67.3</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>544.1</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>66</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>-1.5</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>-9</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>-11</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>-22.4</v>
       </c>
       <c r="O15">
@@ -21228,43 +23267,43 @@
       <c r="A16">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>635.9</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>92.5</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>625.1</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>92.6</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>577.29999999999995</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>73.900000000000006</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>564.9</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>72.5</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>-1.7</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>-9.1999999999999993</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>-2.1</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>-11.2</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>-20.100000000000001</v>
       </c>
       <c r="O16">
@@ -21287,43 +23326,43 @@
       <c r="A17">
         <v>32</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>659.2</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>100.7</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>649.79999999999995</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>99.9</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>597.29999999999995</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>80.400000000000006</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>584.70000000000005</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>78.599999999999994</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>-1.4</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>-9.4</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>-2.1</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <v>-11.3</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>-20.2</v>
       </c>
       <c r="O17">
@@ -21346,43 +23385,43 @@
       <c r="A18">
         <v>34</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>687.2</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>108.1</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>676</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>109.1</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>618.79999999999995</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>87.4</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>608.79999999999995</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>86.2</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>-1.6</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>-10</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>-1.6</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <v>-11.4</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>-19.100000000000001</v>
       </c>
       <c r="O18">
@@ -21405,43 +23444,43 @@
       <c r="A19">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>710.7</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>114.2</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>698.2</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>115.2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>636.9</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>94.7</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>627.4</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>92.3</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>-1.8</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>-10.4</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>-1.5</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <v>-11.7</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>-17.100000000000001</v>
       </c>
       <c r="O19">
@@ -21464,43 +23503,43 @@
       <c r="A20">
         <v>38</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>733.8</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>123</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>722.5</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>123.1</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>655.4</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>101.7</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>644.20000000000005</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>99</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>-1.5</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>-10.7</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>-1.7</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <v>-12.2</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="2">
         <v>-17.3</v>
       </c>
       <c r="O20">
@@ -21523,43 +23562,43 @@
       <c r="A21">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>761.4</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>133.6</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>750.8</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>132.4</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>681.2</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>110.8</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>667.8</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>106.8</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>-1.4</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>-10.5</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>-2</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <v>-12.3</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>-17.100000000000001</v>
       </c>
       <c r="O21">
@@ -21582,43 +23621,43 @@
       <c r="A22">
         <v>60</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>1008</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>231.4</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>991</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>230.4</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>880</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>204.2</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>871.3</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>200.7</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>-1.7</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>-12.7</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>-1</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <v>-13.6</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>-11.8</v>
       </c>
       <c r="O22">
@@ -21641,43 +23680,43 @@
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>1252</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>364.8</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>1235</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>357.1</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>1077.8</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>327.8</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>1066</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>323.5</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="2">
         <v>-1.4</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>-13.9</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <v>-14.9</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>-10.1</v>
       </c>
       <c r="O23">
@@ -21700,43 +23739,43 @@
       <c r="A24">
         <v>100</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>1498.4</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>518.29999999999995</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>1478.6</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>515.4</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>1275.8</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>484.6</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>1265.8</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>478.7</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="2">
         <v>-1.3</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>-14.9</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="2">
         <v>-0.8</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="2">
         <v>-15.5</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>-6.5</v>
       </c>
       <c r="O24">
@@ -21759,43 +23798,43 @@
       <c r="A25">
         <v>120</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>1733.2</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>725.5</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>1714.3</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>715.9</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>1465.8</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>675.5</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>1457</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>670.1</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>-15.4</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="2">
         <v>-0.6</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="2">
         <v>-15.9</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="2">
         <v>-6.9</v>
       </c>
       <c r="O25">
@@ -21818,43 +23857,43 @@
       <c r="A26">
         <v>140</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>1979.5</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>927.9</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>1955.5</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>920.4</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>1661.3</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>884.3</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>1651</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>872</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="2">
         <v>-1.2</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>-16.100000000000001</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="2">
         <v>-0.6</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="2">
         <v>-16.600000000000001</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>-4.7</v>
       </c>
       <c r="O26">
@@ -21877,43 +23916,43 @@
       <c r="A27">
         <v>160</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>2216.1999999999998</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>1183.4000000000001</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>2190.8000000000002</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>1172.0999999999999</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>1849.9</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>1127.0999999999999</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>1838.5</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>1120.8</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>-16.5</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="2">
         <v>-0.6</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="2">
         <v>-17</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>-4.8</v>
       </c>
       <c r="O27">
@@ -21936,43 +23975,43 @@
       <c r="A28">
         <v>180</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>2467</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>1485.6</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>2437</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>1472.7</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>2047.8</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>1409.7</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>2037.2</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>1403.3</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="2">
         <v>-1.2</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>-17</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="2">
         <v>-0.5</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="2">
         <v>-17.399999999999999</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>-5.0999999999999996</v>
       </c>
       <c r="O28">
@@ -21995,43 +24034,43 @@
       <c r="A29">
         <v>200</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>2697.2</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>1771.3</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>2670.1</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>1755</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>2227.1999999999998</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <v>1683.9</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>2214.9</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>1659.5</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="2">
         <v>-1</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>-17.399999999999999</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="2">
         <v>-0.6</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="2">
         <v>-17.899999999999999</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>-4.9000000000000004</v>
       </c>
       <c r="O29">
@@ -22076,7 +24115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371A12C3-65E8-3749-A9AC-304E10D2DC73}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -23728,7 +25767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D884AA-9155-CC4E-B6E2-85DE0BB2105C}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -25380,7 +27419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC04AD51-AFD4-3D42-B2DF-F813173CA207}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/experiments/results.xlsx
+++ b/experiments/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lvuorenk/Documents/vaikkari/paulioptnew/pauliopt/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707D1B80-5C91-E24D-8E35-DF7B4D479676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF60BB9-8A8F-1047-AB02-BDE973443D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="2" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="line6" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="72">
   <si>
     <t>gadgets</t>
   </si>
@@ -249,6 +249,15 @@
   <si>
     <t>pauli strings</t>
   </si>
+  <si>
+    <t>time do</t>
+  </si>
+  <si>
+    <t>time diff</t>
+  </si>
+  <si>
+    <t>time lo</t>
+  </si>
 </sst>
 </file>
 
@@ -257,7 +266,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -394,6 +403,12 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -751,7 +766,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -760,6 +775,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -13632,16 +13652,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17661,1237 +17681,1603 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53CADA0-3FD9-B748-A167-0AF6A36FD04E}">
-  <dimension ref="C3:L44"/>
+  <dimension ref="B1:M45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
+    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.83203125" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" customWidth="1"/>
     <col min="12" max="12" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I1" s="8"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="C3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="D3" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="E3" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
         <v>65</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M3" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
         <v>19</v>
       </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
       <c r="E4">
-        <v>14</v>
+        <v>1488</v>
       </c>
       <c r="F4">
-        <v>1488</v>
+        <v>7641</v>
       </c>
       <c r="G4">
-        <v>7955</v>
+        <v>115.21801499999999</v>
       </c>
       <c r="H4">
         <v>12419</v>
       </c>
       <c r="I4">
-        <v>10850</v>
+        <v>273.029291</v>
+      </c>
+      <c r="J4">
+        <v>10625</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" ref="K4:K19" si="0">G4/H4-1</f>
-        <v>-0.35944923101699011</v>
+        <f>F4/H4-1</f>
+        <v>-0.38473307029551496</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" ref="L4:L19" si="1">I4/G4-1</f>
-        <v>0.36392206159648022</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J4/F4-1</f>
+        <v>0.39052480041879334</v>
+      </c>
+      <c r="M4" s="3">
+        <f>G4/I4-1</f>
+        <v>-0.57800126653810202</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
       <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
         <v>19</v>
       </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
       <c r="E5">
-        <v>14</v>
+        <v>1488</v>
       </c>
       <c r="F5">
-        <v>1488</v>
+        <v>5000</v>
       </c>
       <c r="G5">
-        <v>5059</v>
+        <v>81.148252999999997</v>
       </c>
       <c r="H5">
         <v>12181</v>
       </c>
       <c r="I5">
-        <v>8081</v>
+        <v>284.52725500000003</v>
+      </c>
+      <c r="J5">
+        <v>8085</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.58468106066825376</v>
+        <f>F5/H5-1</f>
+        <v>-0.58952466956735905</v>
       </c>
       <c r="L5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.59735125518877252</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J5/F5-1</f>
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="M5" s="3">
+        <f>G5/I5-1</f>
+        <v>-0.71479620467290561</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
         <v>19</v>
       </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
       <c r="E6">
-        <v>12</v>
+        <v>1085</v>
       </c>
       <c r="F6">
-        <v>1085</v>
+        <v>3133</v>
       </c>
       <c r="G6">
-        <v>3672</v>
+        <v>33.076317000000003</v>
       </c>
       <c r="H6">
         <v>8482</v>
       </c>
       <c r="I6">
-        <v>3058</v>
+        <v>129.12428800000001</v>
+      </c>
+      <c r="J6">
+        <v>3160</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.56708323508606462</v>
-      </c>
-      <c r="L6" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.16721132897603486</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.2">
+        <f>F6/H6-1</f>
+        <v>-0.63062956849799567</v>
+      </c>
+      <c r="L6" s="1">
+        <f>J6/F6-1</f>
+        <v>8.6179380785189608E-3</v>
+      </c>
+      <c r="M6" s="3">
+        <f>G6/I6-1</f>
+        <v>-0.74384124387195072</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
       <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
         <v>22</v>
       </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
       <c r="E7">
-        <v>18</v>
+        <v>2950</v>
       </c>
       <c r="F7">
-        <v>2950</v>
+        <v>21046</v>
       </c>
       <c r="G7">
-        <v>22858</v>
+        <v>461.34287899999998</v>
       </c>
       <c r="H7">
         <v>37786</v>
       </c>
       <c r="I7">
-        <v>15037</v>
+        <v>2522.6866450000002</v>
+      </c>
+      <c r="J7">
+        <v>14622</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.39506695601545549</v>
+        <f>F7/H7-1</f>
+        <v>-0.44302122479225114</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.34215591915303178</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J7/F7-1</f>
+        <v>-0.3052361493870569</v>
+      </c>
+      <c r="M7" s="3">
+        <f>G7/I7-1</f>
+        <v>-0.81712240007517867</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
       <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
         <v>19</v>
       </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
       <c r="E8">
-        <v>14</v>
+        <v>1488</v>
       </c>
       <c r="F8">
-        <v>1488</v>
+        <v>7893</v>
       </c>
       <c r="G8">
-        <v>6958</v>
+        <v>132.73884000000001</v>
       </c>
       <c r="H8">
         <v>12919</v>
       </c>
       <c r="I8">
-        <v>9138</v>
+        <v>346.42907000000002</v>
+      </c>
+      <c r="J8">
+        <v>8778</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.46141342209149316</v>
+        <f>F8/H8-1</f>
+        <v>-0.38903939933431375</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="1"/>
-        <v>0.31330842196033348</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J8/F8-1</f>
+        <v>0.11212466742683391</v>
+      </c>
+      <c r="M8" s="3">
+        <f>G8/I8-1</f>
+        <v>-0.61683688958319816</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
       <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
         <v>19</v>
       </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
       <c r="E9">
-        <v>14</v>
+        <v>1488</v>
       </c>
       <c r="F9">
-        <v>1488</v>
+        <v>10567</v>
       </c>
       <c r="G9">
-        <v>10715</v>
+        <v>161.85106200000001</v>
       </c>
       <c r="H9">
         <v>13433</v>
       </c>
       <c r="I9">
-        <v>6682</v>
+        <v>306.45082100000002</v>
+      </c>
+      <c r="J9">
+        <v>7464</v>
       </c>
       <c r="K9" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.20233752698578134</v>
+        <f>F9/H9-1</f>
+        <v>-0.21335517010347649</v>
       </c>
       <c r="L9" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.37638824078394773</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J9/F9-1</f>
+        <v>-0.29365004258540739</v>
+      </c>
+      <c r="M9" s="3">
+        <f>G9/I9-1</f>
+        <v>-0.47185306447588204</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
         <v>19</v>
       </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
       <c r="E10">
-        <v>12</v>
+        <v>2109</v>
       </c>
       <c r="F10">
-        <v>2109</v>
+        <v>4962</v>
       </c>
       <c r="G10">
-        <v>4975</v>
+        <v>85.607489999999999</v>
       </c>
       <c r="H10">
         <v>14909</v>
       </c>
       <c r="I10">
-        <v>4839</v>
+        <v>560.85743500000001</v>
+      </c>
+      <c r="J10">
+        <v>4532</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.66630894090817627</v>
+        <f>F10/H10-1</f>
+        <v>-0.6671808974444966</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.7336683417085395E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J10/F10-1</f>
+        <v>-8.6658605401047972E-2</v>
+      </c>
+      <c r="M10" s="3">
+        <f>G10/I10-1</f>
+        <v>-0.84736318954209811</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
       <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
         <v>19</v>
       </c>
+      <c r="D11">
+        <v>14</v>
+      </c>
       <c r="E11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="F11">
-        <v>1000</v>
+        <v>5320</v>
       </c>
       <c r="G11">
-        <v>4527</v>
+        <v>49.378607000000002</v>
       </c>
       <c r="H11">
         <v>8675</v>
       </c>
       <c r="I11">
-        <v>7127</v>
+        <v>105.78508100000001</v>
+      </c>
+      <c r="J11">
+        <v>7590</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.47815561959654174</v>
+        <f>F11/H11-1</f>
+        <v>-0.3867435158501441</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.57433178705544519</v>
-      </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J11/F11-1</f>
+        <v>0.42669172932330834</v>
+      </c>
+      <c r="M11" s="3">
+        <f>G11/I11-1</f>
+        <v>-0.53321766610926924</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
         <v>19</v>
       </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
       <c r="E12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="F12">
-        <v>1000</v>
+        <v>4252</v>
       </c>
       <c r="G12">
-        <v>4983</v>
+        <v>36.524329999999999</v>
       </c>
       <c r="H12">
         <v>7967</v>
       </c>
       <c r="I12">
-        <v>3450</v>
+        <v>87.638071999999994</v>
+      </c>
+      <c r="J12">
+        <v>3406</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.37454499811723363</v>
+        <f>F12/H12-1</f>
+        <v>-0.46629848123509476</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.30764599638771828</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J12/F12-1</f>
+        <v>-0.19896519285042336</v>
+      </c>
+      <c r="M12" s="3">
+        <f>G12/I12-1</f>
+        <v>-0.58323672387498438</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
         <v>19</v>
       </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
       <c r="E13">
-        <v>12</v>
+        <v>1085</v>
       </c>
       <c r="F13">
-        <v>1085</v>
+        <v>3222</v>
       </c>
       <c r="G13">
-        <v>3129</v>
+        <v>23.810727</v>
       </c>
       <c r="H13">
         <v>8077</v>
       </c>
       <c r="I13">
-        <v>2872</v>
+        <v>90.031066999999993</v>
+      </c>
+      <c r="J13">
+        <v>2767</v>
       </c>
       <c r="K13" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.6126036894886715</v>
+        <f>F13/H13-1</f>
+        <v>-0.60108951343320538</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="1"/>
-        <v>-8.2134867369766718E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J13/F13-1</f>
+        <v>-0.1412166356300435</v>
+      </c>
+      <c r="M13" s="3">
+        <f>G13/I13-1</f>
+        <v>-0.73552765957999799</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
       <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
         <v>19</v>
       </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
       <c r="E14">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F14">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="G14">
-        <v>298</v>
+        <v>0.19081300000000001</v>
       </c>
       <c r="H14">
         <v>443</v>
       </c>
       <c r="I14">
-        <v>271</v>
+        <v>0.279721</v>
+      </c>
+      <c r="J14">
+        <v>266</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.32731376975169302</v>
+        <f>F14/H14-1</f>
+        <v>-0.34762979683972917</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="1"/>
-        <v>-9.060402684563762E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J14/F14-1</f>
+        <v>-7.9584775086505188E-2</v>
+      </c>
+      <c r="M14" s="3">
+        <f>G14/I14-1</f>
+        <v>-0.31784528154839997</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
       <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
         <v>32</v>
       </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
       <c r="E15">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G15">
-        <v>22</v>
+        <v>1.486E-2</v>
       </c>
       <c r="H15">
         <v>35</v>
       </c>
       <c r="I15">
+        <v>5.5510000000000004E-3</v>
+      </c>
+      <c r="J15">
         <v>24</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="0"/>
+        <f>F15/H15-1</f>
         <v>-0.37142857142857144</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="1"/>
+        <f>J15/F15-1</f>
         <v>9.0909090909090828E-2</v>
       </c>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="7">
+        <f>G15/I15-1</f>
+        <v>1.6769951360115294</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
         <v>19</v>
       </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
       <c r="E16">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F16">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="G16">
-        <v>317</v>
+        <v>0.27967599999999998</v>
       </c>
       <c r="H16">
         <v>414</v>
       </c>
       <c r="I16">
-        <v>267</v>
+        <v>0.30827500000000002</v>
+      </c>
+      <c r="J16">
+        <v>247</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.2342995169082126</v>
+        <f>F16/H16-1</f>
+        <v>-0.21014492753623193</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="1"/>
-        <v>-0.1577287066246057</v>
-      </c>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J16/F16-1</f>
+        <v>-0.24464831804281351</v>
+      </c>
+      <c r="M16" s="3">
+        <f>G16/I16-1</f>
+        <v>-9.2771064796042579E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
       <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
         <v>32</v>
       </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
       <c r="E17">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>1.1167E-2</v>
       </c>
       <c r="H17">
         <v>38</v>
       </c>
       <c r="I17">
+        <v>6.3090000000000004E-3</v>
+      </c>
+      <c r="J17">
         <v>29</v>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="0"/>
+        <f>F17/H17-1</f>
         <v>-0.36842105263157898</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="1"/>
+        <f>J17/F17-1</f>
         <v>0.20833333333333326</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="7">
+        <f>G17/I17-1</f>
+        <v>0.77001109526073841</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
       <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
         <v>36</v>
       </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
       <c r="E18">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="F18">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="G18">
-        <v>235</v>
+        <v>0.26958500000000002</v>
       </c>
       <c r="H18">
         <v>433</v>
       </c>
       <c r="I18">
+        <v>0.34162100000000001</v>
+      </c>
+      <c r="J18">
         <v>215</v>
       </c>
       <c r="K18" s="3">
-        <f t="shared" si="0"/>
-        <v>-0.45727482678983833</v>
+        <f>F18/H18-1</f>
+        <v>-0.45265588914549648</v>
       </c>
       <c r="L18" s="3">
-        <f t="shared" si="1"/>
-        <v>-8.5106382978723416E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+        <f>J18/F18-1</f>
+        <v>-9.2827004219409259E-2</v>
+      </c>
+      <c r="M18" s="3">
+        <f>G18/I18-1</f>
+        <v>-0.210865257112414</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
       <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
         <v>32</v>
       </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>5.1599999999999997E-3</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
+        <v>2.0890000000000001E-3</v>
+      </c>
+      <c r="J19">
         <v>2</v>
       </c>
-      <c r="K19" s="1">
-        <f t="shared" si="0"/>
+      <c r="K19" s="7">
+        <f>F19/H19-1</f>
         <v>0</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="1"/>
+        <f>J19/F19-1</f>
         <v>-0.6</v>
       </c>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="K20" s="1"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="M19" s="7">
+        <f>G19/I19-1</f>
+        <v>1.4700813786500713</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20">
         <v>16</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>1440</v>
+      </c>
+      <c r="F20">
+        <v>11382</v>
+      </c>
+      <c r="G20">
+        <v>164.80469600000001</v>
+      </c>
+      <c r="H20">
+        <v>13852</v>
+      </c>
+      <c r="I20">
+        <v>378.60474699999997</v>
+      </c>
+      <c r="J20">
+        <v>11815</v>
+      </c>
+      <c r="K20" s="3">
+        <f>F20/H20-1</f>
+        <v>-0.17831360092405424</v>
+      </c>
+      <c r="L20" s="1">
+        <f>J20/F20-1</f>
+        <v>3.8042523282375784E-2</v>
+      </c>
+      <c r="M20" s="3">
+        <f>G20/I20-1</f>
+        <v>-0.56470515146499201</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>160</v>
+      </c>
+      <c r="F21">
+        <v>448</v>
+      </c>
+      <c r="G21">
+        <v>0.668852</v>
+      </c>
+      <c r="H21">
+        <v>878</v>
+      </c>
+      <c r="I21">
+        <v>1.1275869999999999</v>
+      </c>
+      <c r="J21">
+        <v>382</v>
+      </c>
+      <c r="K21" s="3">
+        <f>F21/H21-1</f>
+        <v>-0.48974943052391795</v>
+      </c>
+      <c r="L21" s="3">
+        <f>J21/F21-1</f>
+        <v>-0.1473214285714286</v>
+      </c>
+      <c r="M21" s="3">
+        <f>G21/I21-1</f>
+        <v>-0.40682891874418559</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
       <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
         <v>22</v>
       </c>
+      <c r="D22">
+        <v>16</v>
+      </c>
       <c r="E22">
+        <v>1440</v>
+      </c>
+      <c r="F22">
+        <v>11626</v>
+      </c>
+      <c r="G22">
+        <v>165.386697</v>
+      </c>
+      <c r="H22">
+        <v>11727</v>
+      </c>
+      <c r="I22">
+        <v>309.21366599999999</v>
+      </c>
+      <c r="J22">
+        <v>6468</v>
+      </c>
+      <c r="K22" s="3">
+        <f>F22/H22-1</f>
+        <v>-8.6126033938773716E-3</v>
+      </c>
+      <c r="L22" s="3">
+        <f>J22/F22-1</f>
+        <v>-0.44366076036469981</v>
+      </c>
+      <c r="M22" s="3">
+        <f>G22/I22-1</f>
+        <v>-0.46513781509255803</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>160</v>
+      </c>
+      <c r="F23">
+        <v>507</v>
+      </c>
+      <c r="G23">
+        <v>0.79593100000000006</v>
+      </c>
+      <c r="H23">
+        <v>883</v>
+      </c>
+      <c r="I23">
+        <v>1.149607</v>
+      </c>
+      <c r="J23">
+        <v>421</v>
+      </c>
+      <c r="K23" s="3">
+        <f>F23/H23-1</f>
+        <v>-0.42582106455266133</v>
+      </c>
+      <c r="L23" s="3">
+        <f>J23/F23-1</f>
+        <v>-0.16962524654832345</v>
+      </c>
+      <c r="M23" s="3">
+        <f>G23/I23-1</f>
+        <v>-0.30764948369312295</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>2912</v>
+      </c>
+      <c r="F24">
+        <v>15866</v>
+      </c>
+      <c r="G24">
+        <v>318.762201</v>
+      </c>
+      <c r="H24">
+        <v>24224</v>
+      </c>
+      <c r="I24">
+        <v>1493.9029410000001</v>
+      </c>
+      <c r="J24">
+        <v>8374</v>
+      </c>
+      <c r="K24" s="3">
+        <f>F24/H24-1</f>
+        <v>-0.34502972258916775</v>
+      </c>
+      <c r="L24" s="3">
+        <f>J24/F24-1</f>
+        <v>-0.47220471448380186</v>
+      </c>
+      <c r="M24" s="3">
+        <f>G24/I24-1</f>
+        <v>-0.78662455755885685</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>164</v>
+      </c>
+      <c r="F25">
+        <v>217</v>
+      </c>
+      <c r="G25">
+        <v>0.58277299999999999</v>
+      </c>
+      <c r="H25">
+        <v>471</v>
+      </c>
+      <c r="I25">
+        <v>0.57758100000000001</v>
+      </c>
+      <c r="J25">
+        <v>191</v>
+      </c>
+      <c r="K25" s="3">
+        <f>F25/H25-1</f>
+        <v>-0.53927813163481952</v>
+      </c>
+      <c r="L25" s="3">
+        <f>J25/F25-1</f>
+        <v>-0.11981566820276501</v>
+      </c>
+      <c r="M25" s="7">
+        <f>G25/I25-1</f>
+        <v>8.9892153654638207E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26">
         <v>16</v>
       </c>
-      <c r="F22">
-        <v>1440</v>
-      </c>
-      <c r="G22">
-        <v>11580</v>
-      </c>
-      <c r="H22">
-        <v>13852</v>
-      </c>
-      <c r="I22">
-        <v>11196</v>
-      </c>
-      <c r="K22" s="3">
-        <f t="shared" ref="K22:K42" si="2">G22/H22-1</f>
-        <v>-0.16401963615362403</v>
-      </c>
-      <c r="L22" s="3">
-        <f t="shared" ref="L22:L42" si="3">I22/G22-1</f>
-        <v>-3.3160621761658016E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E26">
+        <v>2688</v>
+      </c>
+      <c r="F26">
+        <v>20605</v>
+      </c>
+      <c r="G26">
+        <v>626.60672199999999</v>
+      </c>
+      <c r="H26">
+        <v>28018</v>
+      </c>
+      <c r="I26">
+        <v>1932.4593809999999</v>
+      </c>
+      <c r="J26">
+        <v>11809</v>
+      </c>
+      <c r="K26" s="3">
+        <f>F26/H26-1</f>
+        <v>-0.26457991291312732</v>
+      </c>
+      <c r="L26" s="3">
+        <f>J26/F26-1</f>
+        <v>-0.42688667799077895</v>
+      </c>
+      <c r="M26" s="3">
+        <f>G26/I26-1</f>
+        <v>-0.67574649787684204</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>2688</v>
+      </c>
+      <c r="F27">
+        <v>9143</v>
+      </c>
+      <c r="G27">
+        <v>335.78666199999998</v>
+      </c>
+      <c r="H27">
+        <v>29280</v>
+      </c>
+      <c r="I27">
+        <v>2134.8060519999999</v>
+      </c>
+      <c r="J27">
+        <v>10652</v>
+      </c>
+      <c r="K27" s="3">
+        <f>F27/H27-1</f>
+        <v>-0.68773907103825138</v>
+      </c>
+      <c r="L27" s="1">
+        <f>J27/F27-1</f>
+        <v>0.1650442961828722</v>
+      </c>
+      <c r="M27" s="3">
+        <f>G27/I27-1</f>
+        <v>-0.84270858625053213</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28">
+        <v>20</v>
+      </c>
+      <c r="E28">
+        <v>684</v>
+      </c>
+      <c r="F28">
+        <v>4953</v>
+      </c>
+      <c r="G28">
+        <v>34.247933000000003</v>
+      </c>
+      <c r="H28">
+        <v>6308</v>
+      </c>
+      <c r="I28">
+        <v>60.474814000000002</v>
+      </c>
+      <c r="J28">
+        <v>4740</v>
+      </c>
+      <c r="K28" s="3">
+        <f>F28/H28-1</f>
+        <v>-0.21480659480025366</v>
+      </c>
+      <c r="L28" s="3">
+        <f>J28/F28-1</f>
+        <v>-4.300423985463353E-2</v>
+      </c>
+      <c r="M28" s="3">
+        <f>G28/I28-1</f>
+        <v>-0.43368270632465278</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <v>684</v>
+      </c>
+      <c r="F29">
+        <v>4946</v>
+      </c>
+      <c r="G29">
+        <v>32.466031000000001</v>
+      </c>
+      <c r="H29">
+        <v>5807</v>
+      </c>
+      <c r="I29">
+        <v>55.383809999999997</v>
+      </c>
+      <c r="J29">
+        <v>5704</v>
+      </c>
+      <c r="K29" s="3">
+        <f>F29/H29-1</f>
+        <v>-0.14826933011882215</v>
+      </c>
+      <c r="L29" s="1">
+        <f>J29/F29-1</f>
+        <v>0.15325515568135861</v>
+      </c>
+      <c r="M29" s="3">
+        <f>G29/I29-1</f>
+        <v>-0.41379924927519429</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30">
+        <v>22</v>
+      </c>
+      <c r="E30">
+        <v>3240</v>
+      </c>
+      <c r="F30">
+        <v>42385</v>
+      </c>
+      <c r="G30">
+        <v>1592.0266979999999</v>
+      </c>
+      <c r="H30">
+        <v>35792</v>
+      </c>
+      <c r="I30">
+        <v>3037.7464949999999</v>
+      </c>
+      <c r="J30">
+        <v>47282</v>
+      </c>
+      <c r="K30" s="7">
+        <f>F30/H30-1</f>
+        <v>0.18420317389360741</v>
+      </c>
+      <c r="L30" s="1">
+        <f>J30/F30-1</f>
+        <v>0.11553615665919548</v>
+      </c>
+      <c r="M30" s="3">
+        <f>G30/I30-1</f>
+        <v>-0.47591851373364846</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="E23">
-        <v>8</v>
-      </c>
-      <c r="F23">
-        <v>160</v>
-      </c>
-      <c r="G23">
-        <v>452</v>
-      </c>
-      <c r="H23">
-        <v>878</v>
-      </c>
-      <c r="I23">
-        <v>379</v>
-      </c>
-      <c r="K23" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.48519362186788151</v>
-      </c>
-      <c r="L23" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.16150442477876104</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D31">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>640</v>
+      </c>
+      <c r="F31">
+        <v>2564</v>
+      </c>
+      <c r="G31">
+        <v>15.482094999999999</v>
+      </c>
+      <c r="H31">
+        <v>4250</v>
+      </c>
+      <c r="I31">
+        <v>28.972878999999999</v>
+      </c>
+      <c r="J31">
+        <v>3275</v>
+      </c>
+      <c r="K31" s="3">
+        <f>F31/H31-1</f>
+        <v>-0.39670588235294113</v>
+      </c>
+      <c r="L31" s="1">
+        <f>J31/F31-1</f>
+        <v>0.27730109204368181</v>
+      </c>
+      <c r="M31" s="3">
+        <f>G31/I31-1</f>
+        <v>-0.4656349132580162</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
         <v>22</v>
       </c>
-      <c r="E24">
+      <c r="D32">
+        <v>22</v>
+      </c>
+      <c r="E32">
+        <v>3240</v>
+      </c>
+      <c r="F32">
+        <v>24416</v>
+      </c>
+      <c r="G32">
+        <v>852.84564499999999</v>
+      </c>
+      <c r="H32">
+        <v>33673</v>
+      </c>
+      <c r="I32">
+        <v>3113.253412</v>
+      </c>
+      <c r="J32">
+        <v>16037</v>
+      </c>
+      <c r="K32" s="3">
+        <f>F32/H32-1</f>
+        <v>-0.27490868054524398</v>
+      </c>
+      <c r="L32" s="3">
+        <f>J32/F32-1</f>
+        <v>-0.34317660550458717</v>
+      </c>
+      <c r="M32" s="3">
+        <f>G32/I32-1</f>
+        <v>-0.7260596770848412</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>640</v>
+      </c>
+      <c r="F33">
+        <v>2503</v>
+      </c>
+      <c r="G33">
+        <v>14.346698</v>
+      </c>
+      <c r="H33">
+        <v>4331</v>
+      </c>
+      <c r="I33">
+        <v>29.301047000000001</v>
+      </c>
+      <c r="J33">
+        <v>2336</v>
+      </c>
+      <c r="K33" s="3">
+        <f>F33/H33-1</f>
+        <v>-0.4220734241514662</v>
+      </c>
+      <c r="L33" s="3">
+        <f>J33/F33-1</f>
+        <v>-6.6719936076707897E-2</v>
+      </c>
+      <c r="M33" s="3">
+        <f>G33/I33-1</f>
+        <v>-0.51036910046251927</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
+        <v>630</v>
+      </c>
+      <c r="F34">
+        <v>1432</v>
+      </c>
+      <c r="G34">
+        <v>6.5066259999999998</v>
+      </c>
+      <c r="H34">
+        <v>3472</v>
+      </c>
+      <c r="I34">
+        <v>20.047049999999999</v>
+      </c>
+      <c r="J34">
+        <v>1468</v>
+      </c>
+      <c r="K34" s="3">
+        <f>F34/H34-1</f>
+        <v>-0.5875576036866359</v>
+      </c>
+      <c r="L34" s="1">
+        <f>J34/F34-1</f>
+        <v>2.5139664804469275E-2</v>
+      </c>
+      <c r="M34" s="3">
+        <f>G34/I34-1</f>
+        <v>-0.67543224564212689</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>2950</v>
+      </c>
+      <c r="F35">
+        <v>21728</v>
+      </c>
+      <c r="G35">
+        <v>508.06735300000003</v>
+      </c>
+      <c r="H35">
+        <v>35602</v>
+      </c>
+      <c r="I35">
+        <v>2431.2650039999999</v>
+      </c>
+      <c r="J35">
+        <v>15910</v>
+      </c>
+      <c r="K35" s="3">
+        <f>F35/H35-1</f>
+        <v>-0.38969720802202124</v>
+      </c>
+      <c r="L35" s="3">
+        <f>J35/F35-1</f>
+        <v>-0.2677650957290133</v>
+      </c>
+      <c r="M35" s="3">
+        <f>G35/I35-1</f>
+        <v>-0.79102757117627642</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36">
         <v>16</v>
       </c>
-      <c r="F24">
-        <v>1440</v>
-      </c>
-      <c r="G24">
-        <v>11701</v>
-      </c>
-      <c r="H24">
-        <v>11727</v>
-      </c>
-      <c r="I24">
-        <v>6813</v>
-      </c>
-      <c r="K24" s="1">
-        <f t="shared" si="2"/>
-        <v>-2.2171058241664543E-3</v>
-      </c>
-      <c r="L24" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.41774207332706603</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E36">
+        <v>2340</v>
+      </c>
+      <c r="F36">
+        <v>19534</v>
+      </c>
+      <c r="G36">
+        <v>472.31464199999999</v>
+      </c>
+      <c r="H36">
+        <v>25280</v>
+      </c>
+      <c r="I36">
+        <v>1281.476625</v>
+      </c>
+      <c r="J36">
+        <v>13035</v>
+      </c>
+      <c r="K36" s="3">
+        <f>F36/H36-1</f>
+        <v>-0.2272943037974684</v>
+      </c>
+      <c r="L36" s="3">
+        <f>J36/F36-1</f>
+        <v>-0.33270195556465654</v>
+      </c>
+      <c r="M36" s="3">
+        <f>G36/I36-1</f>
+        <v>-0.63142937390683973</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>2340</v>
+      </c>
+      <c r="F37">
+        <v>9597</v>
+      </c>
+      <c r="G37">
+        <v>222.20063200000001</v>
+      </c>
+      <c r="H37">
+        <v>23182</v>
+      </c>
+      <c r="I37">
+        <v>1149.347585</v>
+      </c>
+      <c r="J37">
+        <v>9670</v>
+      </c>
+      <c r="K37" s="3">
+        <f>F37/H37-1</f>
+        <v>-0.58601501164696745</v>
+      </c>
+      <c r="L37" s="1">
+        <f>J37/F37-1</f>
+        <v>7.6065437115764301E-3</v>
+      </c>
+      <c r="M37" s="3">
+        <f>G37/I37-1</f>
+        <v>-0.8066723810099623</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="E25">
-        <v>8</v>
-      </c>
-      <c r="F25">
-        <v>160</v>
-      </c>
-      <c r="G25">
-        <v>523</v>
-      </c>
-      <c r="H25">
-        <v>883</v>
-      </c>
-      <c r="I25">
-        <v>414</v>
-      </c>
-      <c r="K25" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.40770101925254809</v>
-      </c>
-      <c r="L25" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.20841300191204593</v>
-      </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
+        <v>640</v>
+      </c>
+      <c r="F38">
+        <v>2200</v>
+      </c>
+      <c r="G38">
+        <v>10.826136999999999</v>
+      </c>
+      <c r="H38">
+        <v>4788</v>
+      </c>
+      <c r="I38">
+        <v>27.872985</v>
+      </c>
+      <c r="J38">
+        <v>2461</v>
+      </c>
+      <c r="K38" s="3">
+        <f>F38/H38-1</f>
+        <v>-0.54051796157059318</v>
+      </c>
+      <c r="L38" s="1">
+        <f>J38/F38-1</f>
+        <v>0.11863636363636365</v>
+      </c>
+      <c r="M38" s="3">
+        <f>G38/I38-1</f>
+        <v>-0.61159032661912605</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
         <v>19</v>
       </c>
-      <c r="E26">
-        <v>14</v>
-      </c>
-      <c r="F26">
-        <v>2912</v>
-      </c>
-      <c r="G26">
-        <v>16003</v>
-      </c>
-      <c r="H26">
-        <v>24224</v>
-      </c>
-      <c r="I26">
-        <v>8226</v>
-      </c>
-      <c r="K26" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.33937417437252315</v>
-      </c>
-      <c r="L26" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.48597138036618137</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27">
-        <v>6</v>
-      </c>
-      <c r="F27">
-        <v>164</v>
-      </c>
-      <c r="G27">
-        <v>217</v>
-      </c>
-      <c r="H27">
-        <v>471</v>
-      </c>
-      <c r="I27">
-        <v>191</v>
-      </c>
-      <c r="K27" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.53927813163481952</v>
-      </c>
-      <c r="L27" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.11981566820276501</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28">
-        <v>16</v>
-      </c>
-      <c r="F28">
-        <v>2688</v>
-      </c>
-      <c r="G28">
-        <v>20671</v>
-      </c>
-      <c r="H28">
-        <v>28018</v>
-      </c>
-      <c r="I28">
-        <v>11811</v>
-      </c>
-      <c r="K28" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.26222428438860734</v>
-      </c>
-      <c r="L28" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.42861980552464807</v>
-      </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29">
-        <v>16</v>
-      </c>
-      <c r="F29">
-        <v>2688</v>
-      </c>
-      <c r="G29">
-        <v>9151</v>
-      </c>
-      <c r="H29">
-        <v>29280</v>
-      </c>
-      <c r="I29">
-        <v>10692</v>
-      </c>
-      <c r="K29" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.6874658469945355</v>
-      </c>
-      <c r="L29" s="1">
-        <f t="shared" si="3"/>
-        <v>0.1683968965140421</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30">
-        <v>20</v>
-      </c>
-      <c r="F30">
-        <v>684</v>
-      </c>
-      <c r="G30">
-        <v>4795</v>
-      </c>
-      <c r="H30">
-        <v>6308</v>
-      </c>
-      <c r="I30">
-        <v>5817</v>
-      </c>
-      <c r="K30" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.23985415345592898</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" si="3"/>
-        <v>0.21313868613138687</v>
-      </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31">
-        <v>20</v>
-      </c>
-      <c r="F31">
-        <v>684</v>
-      </c>
-      <c r="G31">
-        <v>4883</v>
-      </c>
-      <c r="H31">
-        <v>5807</v>
-      </c>
-      <c r="I31">
-        <v>5136</v>
-      </c>
-      <c r="K31" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.15911830549337003</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="3"/>
-        <v>5.1812410403440534E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32">
-        <v>22</v>
-      </c>
-      <c r="F32">
-        <v>3240</v>
-      </c>
-      <c r="G32">
-        <v>39569</v>
-      </c>
-      <c r="H32">
-        <v>35792</v>
-      </c>
-      <c r="I32">
-        <v>45769</v>
-      </c>
-      <c r="K32" s="1">
-        <f t="shared" si="2"/>
-        <v>0.10552637460885106</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" si="3"/>
-        <v>0.15668831661148874</v>
-      </c>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D39">
+        <v>12</v>
+      </c>
+      <c r="E39">
+        <v>640</v>
+      </c>
+      <c r="F39">
+        <v>2301</v>
+      </c>
+      <c r="G39">
+        <v>14.329871000000001</v>
+      </c>
+      <c r="H39">
+        <v>4884</v>
+      </c>
+      <c r="I39">
+        <v>32.869433999999998</v>
+      </c>
+      <c r="J39">
+        <v>2415</v>
+      </c>
+      <c r="K39" s="3">
+        <f>F39/H39-1</f>
+        <v>-0.52886977886977893</v>
+      </c>
+      <c r="L39" s="1">
+        <f>J39/F39-1</f>
+        <v>4.9543676662320735E-2</v>
+      </c>
+      <c r="M39" s="3">
+        <f>G39/I39-1</f>
+        <v>-0.56403657574389632</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
         <v>19</v>
       </c>
-      <c r="E33">
-        <v>12</v>
-      </c>
-      <c r="F33">
-        <v>640</v>
-      </c>
-      <c r="G33">
-        <v>2608</v>
-      </c>
-      <c r="H33">
-        <v>4250</v>
-      </c>
-      <c r="I33">
-        <v>3134</v>
-      </c>
-      <c r="K33" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.38635294117647057</v>
-      </c>
-      <c r="L33" s="1">
-        <f t="shared" si="3"/>
-        <v>0.20168711656441718</v>
-      </c>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34">
-        <v>22</v>
-      </c>
-      <c r="F34">
-        <v>3240</v>
-      </c>
-      <c r="G34">
-        <v>26858</v>
-      </c>
-      <c r="H34">
-        <v>33673</v>
-      </c>
-      <c r="I34">
-        <v>15811</v>
-      </c>
-      <c r="K34" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.20238766964630417</v>
-      </c>
-      <c r="L34" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.41131134112741086</v>
-      </c>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35">
-        <v>12</v>
-      </c>
-      <c r="F35">
-        <v>640</v>
-      </c>
-      <c r="G35">
-        <v>2257</v>
-      </c>
-      <c r="H35">
-        <v>4331</v>
-      </c>
-      <c r="I35">
-        <v>2072</v>
-      </c>
-      <c r="K35" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.47887323943661975</v>
-      </c>
-      <c r="L35" s="3">
-        <f t="shared" si="3"/>
-        <v>-8.1967213114754078E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36">
+      <c r="D40">
         <v>10</v>
       </c>
-      <c r="F36">
+      <c r="E40">
         <v>630</v>
       </c>
-      <c r="G36">
-        <v>1458</v>
-      </c>
-      <c r="H36">
+      <c r="F40">
+        <v>1432</v>
+      </c>
+      <c r="G40">
+        <v>6.5269760000000003</v>
+      </c>
+      <c r="H40">
         <v>3472</v>
       </c>
-      <c r="I36">
-        <v>1396</v>
-      </c>
-      <c r="K36" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.58006912442396308</v>
-      </c>
-      <c r="L36" s="3">
-        <f t="shared" si="3"/>
-        <v>-4.2524005486968441E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37">
-        <v>18</v>
-      </c>
-      <c r="F37">
-        <v>2950</v>
-      </c>
-      <c r="G37">
-        <v>16842</v>
-      </c>
-      <c r="H37">
-        <v>35602</v>
-      </c>
-      <c r="I37">
-        <v>15307</v>
-      </c>
-      <c r="K37" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.52693668895005896</v>
-      </c>
-      <c r="L37" s="3">
-        <f t="shared" si="3"/>
-        <v>-9.1141194632466505E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38">
-        <v>16</v>
-      </c>
-      <c r="F38">
-        <v>2340</v>
-      </c>
-      <c r="G38">
-        <v>19767</v>
-      </c>
-      <c r="H38">
-        <v>25280</v>
-      </c>
-      <c r="I38">
-        <v>11460</v>
-      </c>
-      <c r="K38" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.21807753164556964</v>
-      </c>
-      <c r="L38" s="3">
-        <f t="shared" si="3"/>
-        <v>-0.42024586431932009</v>
-      </c>
-    </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39">
-        <v>16</v>
-      </c>
-      <c r="F39">
-        <v>2340</v>
-      </c>
-      <c r="G39">
-        <v>8583</v>
-      </c>
-      <c r="H39">
-        <v>23182</v>
-      </c>
-      <c r="I39">
-        <v>9384</v>
-      </c>
-      <c r="K39" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.62975584505219562</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" si="3"/>
-        <v>9.3324012583013038E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40">
-        <v>12</v>
-      </c>
-      <c r="F40">
-        <v>640</v>
-      </c>
-      <c r="G40">
-        <v>2207</v>
-      </c>
-      <c r="H40">
-        <v>4788</v>
-      </c>
       <c r="I40">
-        <v>2026</v>
+        <v>19.445034</v>
+      </c>
+      <c r="J40">
+        <v>1468</v>
       </c>
       <c r="K40" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.53905597326649957</v>
-      </c>
-      <c r="L40" s="3">
-        <f t="shared" si="3"/>
-        <v>-8.2011780697779812E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41">
-        <v>12</v>
-      </c>
-      <c r="F41">
-        <v>640</v>
-      </c>
-      <c r="G41">
-        <v>2452</v>
-      </c>
-      <c r="H41">
-        <v>4884</v>
-      </c>
-      <c r="I41">
-        <v>2355</v>
-      </c>
-      <c r="K41" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.49795249795249796</v>
-      </c>
-      <c r="L41" s="3">
-        <f t="shared" si="3"/>
-        <v>-3.9559543230016314E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42">
-        <v>10</v>
-      </c>
-      <c r="F42">
-        <v>630</v>
-      </c>
-      <c r="G42">
-        <v>1458</v>
-      </c>
-      <c r="H42">
-        <v>3472</v>
-      </c>
-      <c r="I42">
-        <v>1396</v>
-      </c>
-      <c r="K42" s="3">
-        <f t="shared" si="2"/>
-        <v>-0.58006912442396308</v>
-      </c>
-      <c r="L42" s="3">
-        <f t="shared" si="3"/>
-        <v>-4.2524005486968441E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="K43" s="1"/>
+        <f>F40/H40-1</f>
+        <v>-0.5875576036866359</v>
+      </c>
+      <c r="L40" s="1">
+        <f>J40/F40-1</f>
+        <v>2.5139664804469275E-2</v>
+      </c>
+      <c r="M40" s="3">
+        <f>G40/I40-1</f>
+        <v>-0.66433712586977212</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K41" s="3"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K42" s="3"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K43" s="3"/>
       <c r="L43" s="1"/>
-    </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="K44" s="1"/>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K44" s="3"/>
       <c r="L44" s="1"/>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K45" s="3"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments/results.xlsx
+++ b/experiments/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lvuorenk/Documents/vaikkari/paulioptnew/pauliopt/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF60BB9-8A8F-1047-AB02-BDE973443D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6393EE64-7620-1042-AECD-A6EB1E450755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="2" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="line6" sheetId="1" r:id="rId1"/>
@@ -13652,16 +13652,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/experiments/results.xlsx
+++ b/experiments/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lvuorenk/Documents/vaikkari/paulioptnew/pauliopt/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3980735F-D87F-EB4A-9D36-1823FCDC27CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B213A67D-B99D-A041-99C1-6AA74A35EC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="9" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="12" xr2:uid="{85E89CC3-FE57-2C44-8224-50BF94C0E0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="line6" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="guadalupe depth" sheetId="16" r:id="rId10"/>
     <sheet name="time" sheetId="19" r:id="rId11"/>
     <sheet name="Molecules" sheetId="11" r:id="rId12"/>
+    <sheet name="Molecules_depth" sheetId="20" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="71">
   <si>
     <t>gadgets</t>
   </si>
@@ -77,12 +78,6 @@
   </si>
   <si>
     <t>backend</t>
-  </si>
-  <si>
-    <t>cx do</t>
-  </si>
-  <si>
-    <t>cx dom</t>
   </si>
   <si>
     <t>BeH2_BK_sto3g</t>
@@ -140,9 +135,6 @@
   </si>
   <si>
     <t>nairobi</t>
-  </si>
-  <si>
-    <t>H2_P_sto3g</t>
   </si>
   <si>
     <t>H4_BK_631g</t>
@@ -208,37 +200,16 @@
     <t>NH_P_sto3g</t>
   </si>
   <si>
-    <t>do-&gt;dom</t>
-  </si>
-  <si>
-    <t>molecule</t>
-  </si>
-  <si>
-    <t>qubits</t>
-  </si>
-  <si>
     <t>do + mapping</t>
   </si>
   <si>
     <t>cx lo</t>
   </si>
   <si>
-    <t>lo-&gt;do</t>
-  </si>
-  <si>
     <t>lexicographical ordering</t>
   </si>
   <si>
     <t>lo + mapping</t>
-  </si>
-  <si>
-    <t>pauli strings</t>
-  </si>
-  <si>
-    <t>time do</t>
-  </si>
-  <si>
-    <t>time diff</t>
   </si>
   <si>
     <t>time lo</t>
@@ -264,12 +235,39 @@
   <si>
     <t>guadalupe-16</t>
   </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>num_qubits</t>
+  </si>
+  <si>
+    <t>n_gadgets</t>
+  </si>
+  <si>
+    <t>cx sp</t>
+  </si>
+  <si>
+    <t>time sp</t>
+  </si>
+  <si>
+    <t>cx diff %</t>
+  </si>
+  <si>
+    <t>time diff %</t>
+  </si>
+  <si>
+    <t>qubits</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -406,12 +404,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -769,17 +761,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -2581,10 +2575,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'guadalupe depth'!$A$2:$A$33</c:f>
+              <c:f>'guadalupe depth'!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -2680,16 +2674,25 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'guadalupe depth'!$K$2:$K$33</c:f>
+              <c:f>'guadalupe depth'!$K$2:$K$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2784,6 +2787,15 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2827,10 +2839,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'guadalupe depth'!$A$2:$A$33</c:f>
+              <c:f>'guadalupe depth'!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -2926,16 +2938,25 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'guadalupe depth'!$L$2:$L$33</c:f>
+              <c:f>'guadalupe depth'!$L$2:$L$36</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.95215311004784686</c:v>
                 </c:pt>
@@ -3031,6 +3052,15 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1.0343048515568429</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.0142392344497606</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.0368177929854576</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.0337906270140871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3070,10 +3100,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'guadalupe depth'!$A$2:$A$33</c:f>
+              <c:f>'guadalupe depth'!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3169,16 +3199,25 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'guadalupe depth'!$M$2:$M$33</c:f>
+              <c:f>'guadalupe depth'!$M$2:$M$36</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>1.3995215311004785</c:v>
                 </c:pt>
@@ -3274,6 +3313,15 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1.3015930485155685</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.2650334928229665</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.2702822925577417</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.2619157229229965</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3316,10 +3364,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'guadalupe depth'!$A$2:$A$33</c:f>
+              <c:f>'guadalupe depth'!$A$2:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -3415,16 +3463,25 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'guadalupe depth'!$N$2:$N$33</c:f>
+              <c:f>'guadalupe depth'!$N$2:$N$36</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0.98803827751196172</c:v>
                 </c:pt>
@@ -3520,6 +3577,15 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>1.2998732802317161</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.2591387559808613</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.2674764756201882</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.263603719731148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23626,16 +23692,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -23880,16 +23946,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -23966,16 +24032,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24440,19 +24506,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -26665,6 +26731,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -26703,19 +26770,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -28445,6 +28512,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -28459,38 +28527,38 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>2.5</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>2.3333333333333335</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="3">
         <v>1.2941176470588236</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="3">
         <v>0.78787878787878796</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="3">
         <v>0.8640000000000001</v>
       </c>
     </row>
@@ -28498,19 +28566,19 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>1.736842105263158</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>2.1333333333333333</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>1.0606060606060606</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="3">
         <v>0.7567567567567568</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>0.74725274725274726</v>
       </c>
     </row>
@@ -28518,19 +28586,19 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>1.5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>1.8</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>1.0108695652173914</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="3">
         <v>0.64462809917355368</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>0.67460317460317465</v>
       </c>
     </row>
@@ -28538,19 +28606,19 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>1.3235294117647058</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>1.6666666666666665</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>0.90566037735849059</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>0.60897435897435903</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>0.64353312302839116</v>
       </c>
     </row>
@@ -28558,19 +28626,19 @@
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="3">
         <v>1.2439024390243902</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>1.4374999999999998</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="3">
         <v>0.87121212121212122</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="3">
         <v>0.56509695290858719</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="3">
         <v>0.60212201591511927</v>
       </c>
     </row>
@@ -28578,19 +28646,19 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>1.1020408163265305</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="3">
         <v>1.325</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>0.80536912751677847</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>0.55797101449275366</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>0.5803571428571429</v>
       </c>
     </row>
@@ -28598,19 +28666,19 @@
       <c r="A8">
         <v>14</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>1.0535714285714286</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="3">
         <v>1.24</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>0.78787878787878785</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="3">
         <v>0.55486542443064191</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>0.59081836327345305</v>
       </c>
     </row>
@@ -28618,19 +28686,19 @@
       <c r="A9">
         <v>16</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="3">
         <v>1.015625</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="3">
         <v>1.1538461538461537</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="3">
         <v>0.73134328358208944</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="3">
         <v>0.52602230483271384</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>0.57913043478260862</v>
       </c>
     </row>
@@ -28638,19 +28706,19 @@
       <c r="A10">
         <v>18</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>0.92207792207792205</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>1.1724137931034482</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>0.73148148148148151</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="3">
         <v>0.5160744500846024</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="3">
         <v>0.57650695517774331</v>
       </c>
     </row>
@@ -28658,19 +28726,19 @@
       <c r="A11">
         <v>20</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>1.0634920634920635</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>0.71729957805907174</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="3">
         <v>0.54216867469879515</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="3">
         <v>0.55967078189300401</v>
       </c>
     </row>
@@ -28678,19 +28746,19 @@
       <c r="A12">
         <v>22</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <v>0.92783505154639179</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>1.0144927536231882</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>0.71485943775100413</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="3">
         <v>0.51494565217391308</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="3">
         <v>0.55337423312883438</v>
       </c>
     </row>
@@ -28698,19 +28766,19 @@
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="3">
         <v>0.85470085470085477</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="3">
         <v>1.0370370370370372</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="3">
         <v>0.68953068592057765</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="3">
         <v>0.5216881594372802</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="3">
         <v>0.55239179954441919</v>
       </c>
     </row>
@@ -28718,19 +28786,19 @@
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <v>0.87857142857142867</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>0.95959595959595956</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>0.65972222222222221</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="3">
         <v>0.51995685005393744</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="3">
         <v>0.55233160621761657</v>
       </c>
     </row>
@@ -28738,19 +28806,19 @@
       <c r="A15">
         <v>28</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="3">
         <v>0.85517241379310349</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="3">
         <v>0.94736842105263164</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="3">
         <v>0.64504504504504501</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="3">
         <v>0.50928641251221896</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="3">
         <v>0.53700189753320682</v>
       </c>
     </row>
@@ -28758,19 +28826,19 @@
       <c r="A16">
         <v>30</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>0.83544303797468344</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>0.93661971830985924</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>0.66161616161616155</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="3">
         <v>0.50408719346049047</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="3">
         <v>0.54363001745200701</v>
       </c>
     </row>
@@ -28778,19 +28846,19 @@
       <c r="A17">
         <v>32</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="3">
         <v>0.79899497487437199</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>0.91549295774647887</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="3">
         <v>0.65897435897435896</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="3">
         <v>0.49956784788245456</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="3">
         <v>0.54340836012861726</v>
       </c>
     </row>
@@ -28798,19 +28866,19 @@
       <c r="A18">
         <v>34</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="3">
         <v>0.80327868852459028</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="3">
         <v>0.87179487179487181</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>0.63938053097345127</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="3">
         <v>0.51322314049586781</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="3">
         <v>0.5462610899873257</v>
       </c>
     </row>
@@ -28818,19 +28886,19 @@
       <c r="A19">
         <v>36</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="3">
         <v>0.75824175824175821</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>0.87421383647798745</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="3">
         <v>0.64301552106430149</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="3">
         <v>0.51180502665651173</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="3">
         <v>0.54209183673469385</v>
       </c>
     </row>
@@ -28838,19 +28906,19 @@
       <c r="A20">
         <v>38</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>0.74733096085409245</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>0.86309523809523803</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="3">
         <v>0.64742268041237105</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="3">
         <v>0.51296829971181557</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="3">
         <v>0.54435994930291509</v>
       </c>
     </row>
@@ -28858,19 +28926,19 @@
       <c r="A21">
         <v>40</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <v>0.7432432432432432</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>0.82584269662921339</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="3">
         <v>0.64426877470355737</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="3">
         <v>0.51184834123222744</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="3">
         <v>0.55124317768344455</v>
       </c>
     </row>
@@ -28878,19 +28946,19 @@
       <c r="A22">
         <v>60</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="3">
         <v>0.67621145374449343</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>0.74329501915708807</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="3">
         <v>0.60359408033826645</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="3">
         <v>0.52473704713673541</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="3">
         <v>0.55909389363099149</v>
       </c>
     </row>
@@ -28898,19 +28966,19 @@
       <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>0.61271676300578026</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="3">
         <v>0.69761273209549068</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="3">
         <v>0.58247775496235454</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="3">
         <v>0.54294551510825595</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>0.56645218548923904</v>
       </c>
     </row>
@@ -28918,19 +28986,19 @@
       <c r="A24">
         <v>100</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>0.59046587215601298</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>0.64187866927592951</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="3">
         <v>0.57674199623352163</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="3">
         <v>0.55352257181942544</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>0.56682027649769584</v>
       </c>
     </row>
@@ -28938,19 +29006,19 @@
       <c r="A25">
         <v>120</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>0.56130108423686398</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>0.61310452418096728</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="3">
         <v>0.55918499353169471</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="3">
         <v>0.55544758897121349</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>0.57485936823885764</v>
       </c>
     </row>
@@ -28958,17 +29026,17 @@
       <c r="A26">
         <v>140</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>0.53506620892594403</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>0.59411011523687585</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="3">
         <v>0.54483925549915402</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
         <v>0.57084563292238233</v>
       </c>
     </row>
@@ -28976,17 +29044,17 @@
       <c r="A27">
         <v>160</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="3">
         <v>0.51824431517715497</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>0.54211663066954641</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="3">
         <v>0.53127354935945748</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3">
         <v>0.56874999999999998</v>
       </c>
     </row>
@@ -28994,17 +29062,17 @@
       <c r="A28">
         <v>180</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="3">
         <v>0.49758454106280192</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="3">
         <v>0.54637436762225966</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="3">
         <v>0.52087336244541482</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7">
+      <c r="E28" s="3"/>
+      <c r="F28" s="3">
         <v>0.5660663918420481</v>
       </c>
     </row>
@@ -29012,17 +29080,17 @@
       <c r="A29">
         <v>200</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="3">
         <v>0.48476257973068754</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="3">
         <v>0.53048297703879654</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="3">
         <v>0.51155984781972497</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7">
+      <c r="E29" s="3"/>
+      <c r="F29" s="3">
         <v>0.56240763133145233</v>
       </c>
     </row>
@@ -29030,19 +29098,19 @@
       <c r="A30">
         <v>300</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="3">
         <v>0.42991936867387204</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="3">
         <v>0.48534635879218474</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="3">
         <v>0.4594255529877847</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="3">
         <v>0.53531684519815836</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="3">
         <v>0.53698829260627012</v>
       </c>
     </row>
@@ -29050,55 +29118,55 @@
       <c r="A31">
         <v>400</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="3">
         <v>0.38625670204617574</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="3">
         <v>0.45255474452554745</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="3">
         <v>0.4214340899893308</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="3">
         <v>0.51437764606265879</v>
       </c>
-      <c r="F31" s="7"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>500</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="3">
         <v>0.3572403822986106</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="3">
         <v>0.43067484662576688</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="3">
         <v>0.38760746487733277</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="3">
         <v>0.48131612515945071</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>600</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="3">
         <v>0.3376307034220532</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="3">
         <v>0.40670721683379918</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="3">
         <v>0.35851828197349517</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="3">
         <v>0.45146402038010164</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="3">
         <v>0.45182562722745406</v>
       </c>
     </row>
@@ -29106,19 +29174,19 @@
       <c r="A34">
         <v>700</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="3">
         <v>0.31706750858946975</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="3">
         <v>0.39116125999059709</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="3">
         <v>0.33258963949136222</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="3">
         <v>0.42834042871013522</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="3">
         <v>0.37701705374640371</v>
       </c>
     </row>
@@ -29126,19 +29194,19 @@
       <c r="A35">
         <v>800</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="3">
         <v>0.29839948128178001</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="3">
         <v>0.37948512738428702</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="3">
         <v>0.31196698762035763</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="3">
         <v>0.40866185738532029</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="3">
         <v>0.40040707695300909</v>
       </c>
     </row>
@@ -29146,14 +29214,14 @@
       <c r="A36">
         <v>900</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="3">
         <v>0.28536254737599248</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="3">
         <v>0.36676182201812085</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="F36" s="7">
+      <c r="D36" s="3"/>
+      <c r="F36" s="3">
         <v>0.37761479638239509</v>
       </c>
     </row>
@@ -29161,25 +29229,25 @@
       <c r="A37">
         <v>1000</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="3">
         <v>0.27427818258685438</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="3">
         <v>0.35405657444824368</v>
       </c>
-      <c r="D37" s="7"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1100</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="3">
         <v>0.26047296471106107</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="3">
         <v>0.34936759286923613</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="3">
         <v>0.25881910297494715</v>
       </c>
     </row>
@@ -29187,10 +29255,10 @@
       <c r="A39">
         <v>1200</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="3">
         <v>0.25179586482603533</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="3">
         <v>0.34108729743857819</v>
       </c>
     </row>
@@ -29198,10 +29266,10 @@
       <c r="A40">
         <v>1300</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="3">
         <v>0.24467687074829933</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="3">
         <v>0.33322784810126582</v>
       </c>
     </row>
@@ -29209,10 +29277,10 @@
       <c r="A41">
         <v>1400</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="3">
         <v>0.23727919852359608</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="3">
         <v>0.33004791238877479</v>
       </c>
     </row>
@@ -29220,10 +29288,10 @@
       <c r="A42">
         <v>1500</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="3">
         <v>0.23019002734305227</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="3">
         <v>0.32086687306501549</v>
       </c>
     </row>
@@ -29231,8 +29299,8 @@
       <c r="A43">
         <v>1600</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3">
         <v>0.31543921916592726</v>
       </c>
     </row>
@@ -29240,8 +29308,8 @@
       <c r="A44">
         <v>1700</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3">
         <v>0.3135810926528515</v>
       </c>
     </row>
@@ -29249,10 +29317,10 @@
       <c r="A45">
         <v>1800</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="3">
         <v>0.21461160562284157</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="3">
         <v>0.30778420523138833</v>
       </c>
     </row>
@@ -29260,1630 +29328,2169 @@
       <c r="A46">
         <v>1900</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="3">
         <v>0.20966088777146061</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="3">
         <v>0.30111699000587894</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B47" s="7"/>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B48" s="7"/>
+      <c r="B48" s="3"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="7"/>
+      <c r="B49" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53CADA0-3FD9-B748-A167-0AF6A36FD04E}">
-  <dimension ref="B1:M45"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="5.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="I1" s="6"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="I1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="4">
+        <v>-37.14</v>
+      </c>
+      <c r="J2" s="4">
+        <v>-25.69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>0.01</v>
+      </c>
+      <c r="G3">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="4">
+        <v>-31.58</v>
+      </c>
+      <c r="J3" s="4">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>84</v>
+      </c>
+      <c r="E4">
+        <v>289</v>
+      </c>
+      <c r="F4">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G4">
+        <v>443</v>
+      </c>
+      <c r="H4">
+        <v>0.23</v>
+      </c>
+      <c r="I4" s="4">
+        <v>-34.76</v>
+      </c>
+      <c r="J4" s="4">
+        <v>-41.52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>84</v>
+      </c>
+      <c r="E5">
+        <v>291</v>
+      </c>
+      <c r="F5">
+        <v>0.16</v>
+      </c>
+      <c r="G5">
+        <v>414</v>
+      </c>
+      <c r="H5">
+        <v>0.3</v>
+      </c>
+      <c r="I5" s="4">
+        <v>-29.71</v>
+      </c>
+      <c r="J5" s="4">
+        <v>-47.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>158</v>
+      </c>
+      <c r="E6">
+        <v>222</v>
+      </c>
+      <c r="F6">
+        <v>0.18</v>
+      </c>
+      <c r="G6">
+        <v>433</v>
+      </c>
+      <c r="H6">
+        <v>0.36</v>
+      </c>
+      <c r="I6" s="4">
+        <v>-48.73</v>
+      </c>
+      <c r="J6" s="4">
+        <v>-49.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>160</v>
+      </c>
+      <c r="E7">
+        <v>443</v>
+      </c>
+      <c r="F7">
+        <v>0.47</v>
+      </c>
+      <c r="G7">
+        <v>878</v>
+      </c>
+      <c r="H7">
+        <v>1.17</v>
+      </c>
+      <c r="I7" s="4">
+        <v>-49.54</v>
+      </c>
+      <c r="J7" s="4">
+        <v>-59.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>160</v>
+      </c>
+      <c r="E8">
+        <v>470</v>
+      </c>
+      <c r="F8">
+        <v>0.51</v>
+      </c>
+      <c r="G8">
+        <v>883</v>
+      </c>
+      <c r="H8">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I8" s="4">
+        <v>-46.77</v>
+      </c>
+      <c r="J8" s="4">
+        <v>-54.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>164</v>
+      </c>
+      <c r="E9">
+        <v>213</v>
+      </c>
+      <c r="F9">
+        <v>0.21</v>
+      </c>
+      <c r="G9">
+        <v>471</v>
+      </c>
+      <c r="H9">
+        <v>0.36</v>
+      </c>
+      <c r="I9" s="4">
+        <v>-54.78</v>
+      </c>
+      <c r="J9" s="4">
+        <v>-41.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="D10">
+        <v>630</v>
+      </c>
+      <c r="E10">
+        <v>1288</v>
+      </c>
+      <c r="F10">
+        <v>3.66</v>
+      </c>
+      <c r="G10">
+        <v>3472</v>
+      </c>
+      <c r="H10">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="I10" s="4">
+        <v>-62.9</v>
+      </c>
+      <c r="J10" s="4">
+        <v>-80.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>630</v>
+      </c>
+      <c r="E11">
+        <v>1288</v>
+      </c>
+      <c r="F11">
+        <v>3.9</v>
+      </c>
+      <c r="G11">
+        <v>3472</v>
+      </c>
+      <c r="H11">
+        <v>19.77</v>
+      </c>
+      <c r="I11" s="4">
+        <v>-62.9</v>
+      </c>
+      <c r="J11" s="4">
+        <v>-80.290000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>640</v>
+      </c>
+      <c r="E12">
+        <v>2659</v>
+      </c>
+      <c r="F12">
+        <v>11.79</v>
+      </c>
+      <c r="G12">
+        <v>4250</v>
+      </c>
+      <c r="H12">
+        <v>30.84</v>
+      </c>
+      <c r="I12" s="4">
+        <v>-37.44</v>
+      </c>
+      <c r="J12" s="4">
+        <v>-61.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>640</v>
+      </c>
+      <c r="E13">
+        <v>1924</v>
+      </c>
+      <c r="F13">
+        <v>8.74</v>
+      </c>
+      <c r="G13">
+        <v>4331</v>
+      </c>
+      <c r="H13">
+        <v>29.67</v>
+      </c>
+      <c r="I13" s="4">
+        <v>-55.58</v>
+      </c>
+      <c r="J13" s="4">
+        <v>-70.53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>640</v>
+      </c>
+      <c r="E14">
+        <v>2092</v>
+      </c>
+      <c r="F14">
+        <v>6.93</v>
+      </c>
+      <c r="G14">
+        <v>4788</v>
+      </c>
+      <c r="H14">
+        <v>25.3</v>
+      </c>
+      <c r="I14" s="4">
+        <v>-56.31</v>
+      </c>
+      <c r="J14" s="4">
+        <v>-72.599999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>640</v>
+      </c>
+      <c r="E15">
+        <v>1969</v>
+      </c>
+      <c r="F15">
+        <v>8.5</v>
+      </c>
+      <c r="G15">
+        <v>4884</v>
+      </c>
+      <c r="H15">
+        <v>32.04</v>
+      </c>
+      <c r="I15" s="4">
+        <v>-59.68</v>
+      </c>
+      <c r="J15" s="4">
+        <v>-73.47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>684</v>
+      </c>
+      <c r="E16">
+        <v>2918</v>
+      </c>
+      <c r="F16">
+        <v>11.97</v>
+      </c>
+      <c r="G16">
+        <v>6308</v>
+      </c>
+      <c r="H16">
+        <v>50.09</v>
+      </c>
+      <c r="I16" s="4">
+        <v>-53.74</v>
+      </c>
+      <c r="J16" s="4">
+        <v>-76.099999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>684</v>
+      </c>
+      <c r="E17">
+        <v>3409</v>
+      </c>
+      <c r="F17">
+        <v>12.65</v>
+      </c>
+      <c r="G17">
+        <v>5807</v>
+      </c>
+      <c r="H17">
+        <v>44.81</v>
+      </c>
+      <c r="I17" s="4">
+        <v>-41.29</v>
+      </c>
+      <c r="J17" s="4">
+        <v>-71.78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="8">
+        <v>14</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3856</v>
+      </c>
+      <c r="F18" s="8">
+        <v>25.27</v>
+      </c>
+      <c r="G18" s="8">
+        <v>8675</v>
+      </c>
+      <c r="H18" s="8">
+        <v>102.91</v>
+      </c>
+      <c r="I18" s="9">
+        <v>-55.55</v>
+      </c>
+      <c r="J18" s="9">
+        <v>-75.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="6">
+        <v>14</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3633</v>
+      </c>
+      <c r="F19" s="6">
+        <v>18.29</v>
+      </c>
+      <c r="G19" s="6">
+        <v>7967</v>
+      </c>
+      <c r="H19" s="6">
+        <v>78.69</v>
+      </c>
+      <c r="I19" s="7">
+        <v>-54.4</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-76.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>1085</v>
+      </c>
+      <c r="E22">
+        <v>2904</v>
+      </c>
+      <c r="F22">
+        <v>12.52</v>
+      </c>
+      <c r="G22">
+        <v>8482</v>
+      </c>
+      <c r="H22">
+        <v>85.23</v>
+      </c>
+      <c r="I22" s="4">
+        <v>-65.760000000000005</v>
+      </c>
+      <c r="J22" s="4">
+        <v>-85.31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23">
+        <v>1085</v>
+      </c>
+      <c r="E23">
+        <v>2704</v>
+      </c>
+      <c r="F23">
+        <v>12.73</v>
+      </c>
+      <c r="G23">
+        <v>8077</v>
+      </c>
+      <c r="H23">
+        <v>94.79</v>
+      </c>
+      <c r="I23" s="4">
+        <v>-66.52</v>
+      </c>
+      <c r="J23" s="4">
+        <v>-86.57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>1440</v>
+      </c>
+      <c r="E24">
+        <v>7115</v>
+      </c>
+      <c r="F24">
+        <v>54.93</v>
+      </c>
+      <c r="G24">
+        <v>13852</v>
+      </c>
+      <c r="H24">
+        <v>307.7</v>
+      </c>
+      <c r="I24" s="4">
+        <v>-48.64</v>
+      </c>
+      <c r="J24" s="4">
+        <v>-82.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>1440</v>
+      </c>
+      <c r="E25">
+        <v>5453</v>
+      </c>
+      <c r="F25">
+        <v>57.79</v>
+      </c>
+      <c r="G25">
+        <v>11727</v>
+      </c>
+      <c r="H25">
+        <v>314.38</v>
+      </c>
+      <c r="I25" s="4">
+        <v>-53.5</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-81.62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>1488</v>
+      </c>
+      <c r="E26">
+        <v>6689</v>
+      </c>
+      <c r="F26">
+        <v>52.05</v>
+      </c>
+      <c r="G26">
+        <v>12419</v>
+      </c>
+      <c r="H26">
+        <v>225.43</v>
+      </c>
+      <c r="I26" s="4">
+        <v>-46.14</v>
+      </c>
+      <c r="J26" s="4">
+        <v>-76.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>1488</v>
+      </c>
+      <c r="E27">
+        <v>5190</v>
+      </c>
+      <c r="F27">
+        <v>48.34</v>
+      </c>
+      <c r="G27">
+        <v>12181</v>
+      </c>
+      <c r="H27">
+        <v>268.23</v>
+      </c>
+      <c r="I27" s="4">
+        <v>-57.39</v>
+      </c>
+      <c r="J27" s="4">
+        <v>-81.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+      <c r="D28">
+        <v>1488</v>
+      </c>
+      <c r="E28">
+        <v>5802</v>
+      </c>
+      <c r="F28">
+        <v>45.46</v>
+      </c>
+      <c r="G28">
+        <v>12919</v>
+      </c>
+      <c r="H28">
+        <v>241.44</v>
+      </c>
+      <c r="I28" s="4">
+        <v>-55.09</v>
+      </c>
+      <c r="J28" s="4">
+        <v>-81.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>1488</v>
+      </c>
+      <c r="E29">
+        <v>4874</v>
+      </c>
+      <c r="F29">
+        <v>41.69</v>
+      </c>
+      <c r="G29">
+        <v>13433</v>
+      </c>
+      <c r="H29">
+        <v>253.96</v>
+      </c>
+      <c r="I29" s="4">
+        <v>-63.72</v>
+      </c>
+      <c r="J29" s="4">
+        <v>-83.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <v>2109</v>
+      </c>
+      <c r="E30">
+        <v>4609</v>
+      </c>
+      <c r="F30">
+        <v>35.71</v>
+      </c>
+      <c r="G30">
+        <v>14909</v>
+      </c>
+      <c r="H30">
+        <v>412.24</v>
+      </c>
+      <c r="I30" s="4">
+        <v>-69.09</v>
+      </c>
+      <c r="J30" s="4">
+        <v>-91.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>2340</v>
+      </c>
+      <c r="E31">
+        <v>8953</v>
+      </c>
+      <c r="F31">
+        <v>149.62</v>
+      </c>
+      <c r="G31">
+        <v>25280</v>
+      </c>
+      <c r="H31">
+        <v>1347.44</v>
+      </c>
+      <c r="I31" s="4">
+        <v>-64.58</v>
+      </c>
+      <c r="J31" s="4">
+        <v>-88.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>2340</v>
+      </c>
+      <c r="E32">
+        <v>8473</v>
+      </c>
+      <c r="F32">
+        <v>134.43</v>
+      </c>
+      <c r="G32">
+        <v>23182</v>
+      </c>
+      <c r="H32">
+        <v>7368.92</v>
+      </c>
+      <c r="I32" s="4">
+        <v>-63.45</v>
+      </c>
+      <c r="J32" s="4">
+        <v>-98.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>2688</v>
+      </c>
+      <c r="E33">
+        <v>10730</v>
+      </c>
+      <c r="F33">
+        <v>196.15</v>
+      </c>
+      <c r="G33">
+        <v>28018</v>
+      </c>
+      <c r="H33">
+        <v>1787.52</v>
+      </c>
+      <c r="I33" s="4">
+        <v>-61.7</v>
+      </c>
+      <c r="J33" s="4">
+        <v>-89.03</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>16</v>
+      </c>
+      <c r="D34">
+        <v>2688</v>
+      </c>
+      <c r="E34">
+        <v>9435</v>
+      </c>
+      <c r="F34">
+        <v>152.34</v>
+      </c>
+      <c r="G34">
+        <v>29280</v>
+      </c>
+      <c r="H34">
+        <v>1806.2</v>
+      </c>
+      <c r="I34" s="4">
+        <v>-67.78</v>
+      </c>
+      <c r="J34" s="4">
+        <v>-91.57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
+        <v>2912</v>
+      </c>
+      <c r="E35">
+        <v>7878</v>
+      </c>
+      <c r="F35">
+        <v>90.18</v>
+      </c>
+      <c r="G35">
+        <v>24224</v>
+      </c>
+      <c r="H35">
+        <v>1275.78</v>
+      </c>
+      <c r="I35" s="4">
+        <v>-67.48</v>
+      </c>
+      <c r="J35" s="4">
+        <v>-92.93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>18</v>
+      </c>
+      <c r="D36">
+        <v>2950</v>
+      </c>
+      <c r="E36">
+        <v>12170</v>
+      </c>
+      <c r="F36">
+        <v>177.65</v>
+      </c>
+      <c r="G36">
+        <v>37786</v>
+      </c>
+      <c r="H36">
+        <v>8568.33</v>
+      </c>
+      <c r="I36" s="4">
+        <v>-67.790000000000006</v>
+      </c>
+      <c r="J36" s="4">
+        <v>-97.93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>18</v>
+      </c>
+      <c r="D37">
+        <v>2950</v>
+      </c>
+      <c r="E37">
+        <v>12144</v>
+      </c>
+      <c r="F37">
+        <v>165.51</v>
+      </c>
+      <c r="G37">
+        <v>35602</v>
+      </c>
+      <c r="H37">
+        <v>2334.06</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-65.89</v>
+      </c>
+      <c r="J37" s="4">
+        <v>-92.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>22</v>
+      </c>
+      <c r="D38">
+        <v>3240</v>
+      </c>
+      <c r="E38">
+        <v>25510</v>
+      </c>
+      <c r="F38">
+        <v>551.54</v>
+      </c>
+      <c r="G38">
+        <v>35792</v>
+      </c>
+      <c r="H38">
+        <v>3240.58</v>
+      </c>
+      <c r="I38" s="4">
+        <v>-28.73</v>
+      </c>
+      <c r="J38" s="4">
+        <v>-82.98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="6">
+        <v>22</v>
+      </c>
+      <c r="D39" s="6">
+        <v>3240</v>
+      </c>
+      <c r="E39" s="6">
+        <v>14668</v>
+      </c>
+      <c r="F39" s="6">
+        <v>299.52999999999997</v>
+      </c>
+      <c r="G39" s="6">
+        <v>33673</v>
+      </c>
+      <c r="H39" s="6">
+        <v>2840.07</v>
+      </c>
+      <c r="I39" s="7">
+        <v>-56.44</v>
+      </c>
+      <c r="J39" s="7">
+        <v>-89.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I40" s="2"/>
+      <c r="J40" s="1"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J47">
+    <sortCondition ref="D1:D47"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A422EB-FC22-9C4C-B0A9-035F39BC9786}">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="E1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>12</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="E2">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>35</v>
+      </c>
+      <c r="G2" s="4">
+        <v>-37.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>38</v>
+      </c>
+      <c r="G3" s="4">
+        <v>-31.58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>84</v>
+      </c>
+      <c r="E4">
+        <v>196</v>
+      </c>
+      <c r="F4">
+        <v>301</v>
+      </c>
+      <c r="G4" s="4">
+        <v>-34.880000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>84</v>
+      </c>
+      <c r="E5">
+        <v>207</v>
+      </c>
+      <c r="F5">
+        <v>272</v>
+      </c>
+      <c r="G5" s="4">
+        <v>-23.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>158</v>
+      </c>
+      <c r="E6">
+        <v>169</v>
+      </c>
+      <c r="F6">
+        <v>332</v>
+      </c>
+      <c r="G6" s="4">
+        <v>-49.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>160</v>
+      </c>
+      <c r="E7">
+        <v>307</v>
+      </c>
+      <c r="F7">
+        <v>523</v>
+      </c>
+      <c r="G7" s="4">
+        <v>-41.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>160</v>
+      </c>
+      <c r="E8">
+        <v>331</v>
+      </c>
+      <c r="F8">
+        <v>552</v>
+      </c>
+      <c r="G8" s="4">
+        <v>-40.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>164</v>
+      </c>
+      <c r="E9">
+        <v>177</v>
+      </c>
+      <c r="F9">
+        <v>344</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-48.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>630</v>
+      </c>
+      <c r="E10">
+        <v>841</v>
+      </c>
+      <c r="F10">
+        <v>1933</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-56.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>630</v>
+      </c>
+      <c r="E11">
+        <v>841</v>
+      </c>
+      <c r="F11">
+        <v>1933</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-56.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>640</v>
+      </c>
+      <c r="E12">
+        <v>1599</v>
+      </c>
+      <c r="F12">
+        <v>2261</v>
+      </c>
+      <c r="G12" s="4">
+        <v>-29.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>640</v>
+      </c>
+      <c r="E13">
+        <v>1155</v>
+      </c>
+      <c r="F13">
+        <v>2385</v>
+      </c>
+      <c r="G13" s="4">
+        <v>-51.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>640</v>
+      </c>
+      <c r="E14">
+        <v>1313</v>
+      </c>
+      <c r="F14">
+        <v>2433</v>
+      </c>
+      <c r="G14" s="4">
+        <v>-46.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>640</v>
+      </c>
+      <c r="E15">
+        <v>1213</v>
+      </c>
+      <c r="F15">
+        <v>2608</v>
+      </c>
+      <c r="G15" s="4">
+        <v>-53.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>684</v>
+      </c>
+      <c r="E16">
+        <v>1636</v>
+      </c>
+      <c r="F16">
+        <v>2712</v>
+      </c>
+      <c r="G16" s="4">
+        <v>-39.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>684</v>
+      </c>
+      <c r="E17">
+        <v>1904</v>
+      </c>
+      <c r="F17">
+        <v>2677</v>
+      </c>
+      <c r="G17" s="4">
+        <v>-28.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
+      </c>
+      <c r="E18">
+        <v>2212</v>
+      </c>
+      <c r="F18">
+        <v>3877</v>
+      </c>
+      <c r="G18" s="4">
+        <v>-42.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="6">
+        <v>14</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2086</v>
+      </c>
+      <c r="F19" s="6">
+        <v>3683</v>
+      </c>
+      <c r="G19" s="7">
+        <v>-43.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>1085</v>
+      </c>
+      <c r="E22">
+        <v>1824</v>
+      </c>
+      <c r="F22">
+        <v>4372</v>
+      </c>
+      <c r="G22" s="4">
+        <v>-58.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23">
+        <v>1085</v>
+      </c>
+      <c r="E23">
+        <v>1689</v>
+      </c>
+      <c r="F23">
+        <v>4015</v>
+      </c>
+      <c r="G23" s="4">
+        <v>-57.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>1440</v>
+      </c>
+      <c r="E24">
+        <v>4097</v>
+      </c>
+      <c r="F24">
+        <v>4585</v>
+      </c>
+      <c r="G24" s="4">
+        <v>-10.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>1440</v>
+      </c>
+      <c r="E25">
+        <v>3072</v>
+      </c>
+      <c r="F25">
+        <v>5267</v>
+      </c>
+      <c r="G25" s="4">
+        <v>-41.67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>1488</v>
+      </c>
+      <c r="E26">
+        <v>4020</v>
+      </c>
+      <c r="F26">
+        <v>5628</v>
+      </c>
+      <c r="G26" s="4">
+        <v>-28.57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
         <v>14</v>
       </c>
-      <c r="D4">
+      <c r="D27">
+        <v>1488</v>
+      </c>
+      <c r="E27">
+        <v>2928</v>
+      </c>
+      <c r="F27">
+        <v>5908</v>
+      </c>
+      <c r="G27" s="4">
+        <v>-50.44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
         <v>14</v>
       </c>
-      <c r="E4">
+      <c r="D28">
         <v>1488</v>
       </c>
-      <c r="F4">
-        <v>7641</v>
-      </c>
-      <c r="G4">
-        <v>115.21801499999999</v>
-      </c>
-      <c r="H4">
-        <v>12419</v>
-      </c>
-      <c r="I4">
-        <v>273.029291</v>
-      </c>
-      <c r="J4">
-        <v>10625</v>
-      </c>
-      <c r="K4" s="2">
-        <f t="shared" ref="K4:K40" si="0">F4/H4-1</f>
-        <v>-0.38473307029551496</v>
-      </c>
-      <c r="L4" s="1">
-        <f t="shared" ref="L4:L40" si="1">J4/F4-1</f>
-        <v>0.39052480041879334</v>
-      </c>
-      <c r="M4" s="2">
-        <f t="shared" ref="M4:M40" si="2">G4/I4-1</f>
-        <v>-0.57800126653810202</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="E28">
+        <v>3330</v>
+      </c>
+      <c r="F28">
+        <v>6182</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-46.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>1488</v>
+      </c>
+      <c r="E29">
+        <v>2801</v>
+      </c>
+      <c r="F29">
+        <v>6398</v>
+      </c>
+      <c r="G29" s="4">
+        <v>-56.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <v>2109</v>
+      </c>
+      <c r="E30">
+        <v>2703</v>
+      </c>
+      <c r="F30">
+        <v>7740</v>
+      </c>
+      <c r="G30" s="4">
+        <v>-65.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>2340</v>
+      </c>
+      <c r="E31">
+        <v>5174</v>
+      </c>
+      <c r="F31">
+        <v>8400</v>
+      </c>
+      <c r="G31" s="4">
+        <v>-38.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>2340</v>
+      </c>
+      <c r="E32">
+        <v>4651</v>
+      </c>
+      <c r="F32">
+        <v>7937</v>
+      </c>
+      <c r="G32" s="4">
+        <v>-41.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>2688</v>
+      </c>
+      <c r="E33">
+        <v>6123</v>
+      </c>
+      <c r="F33">
+        <v>9355</v>
+      </c>
+      <c r="G33" s="4">
+        <v>-34.549999999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>16</v>
+      </c>
+      <c r="D34">
+        <v>2688</v>
+      </c>
+      <c r="E34">
+        <v>5401</v>
+      </c>
+      <c r="F34">
+        <v>9118</v>
+      </c>
+      <c r="G34" s="4">
+        <v>-40.770000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>1488</v>
-      </c>
-      <c r="F5">
-        <v>5000</v>
-      </c>
-      <c r="G5">
-        <v>81.148252999999997</v>
-      </c>
-      <c r="H5">
-        <v>12181</v>
-      </c>
-      <c r="I5">
-        <v>284.52725500000003</v>
-      </c>
-      <c r="J5">
-        <v>8085</v>
-      </c>
-      <c r="K5" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.58952466956735905</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.61699999999999999</v>
-      </c>
-      <c r="M5" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.71479620467290561</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="D35">
+        <v>2912</v>
+      </c>
+      <c r="E35">
+        <v>4331</v>
+      </c>
+      <c r="F35">
+        <v>10984</v>
+      </c>
+      <c r="G35" s="4">
+        <v>-60.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>1085</v>
-      </c>
-      <c r="F6">
-        <v>3133</v>
-      </c>
-      <c r="G6">
-        <v>33.076317000000003</v>
-      </c>
-      <c r="H6">
-        <v>8482</v>
-      </c>
-      <c r="I6">
-        <v>129.12428800000001</v>
-      </c>
-      <c r="J6">
-        <v>3160</v>
-      </c>
-      <c r="K6" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.63062956849799567</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="1"/>
-        <v>8.6179380785189608E-3</v>
-      </c>
-      <c r="M6" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.74384124387195072</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7">
+      <c r="D36">
+        <v>2950</v>
+      </c>
+      <c r="E36">
+        <v>6641</v>
+      </c>
+      <c r="F36">
+        <v>11144</v>
+      </c>
+      <c r="G36" s="4">
+        <v>-40.409999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
         <v>18</v>
       </c>
-      <c r="E7">
+      <c r="D37">
         <v>2950</v>
       </c>
-      <c r="F7">
-        <v>21046</v>
-      </c>
-      <c r="G7">
-        <v>461.34287899999998</v>
-      </c>
-      <c r="H7">
-        <v>37786</v>
-      </c>
-      <c r="I7">
-        <v>2522.6866450000002</v>
-      </c>
-      <c r="J7">
-        <v>14622</v>
-      </c>
-      <c r="K7" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.44302122479225114</v>
-      </c>
-      <c r="L7" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.3052361493870569</v>
-      </c>
-      <c r="M7" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.81712240007517867</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>1488</v>
-      </c>
-      <c r="F8">
-        <v>7893</v>
-      </c>
-      <c r="G8">
-        <v>132.73884000000001</v>
-      </c>
-      <c r="H8">
-        <v>12919</v>
-      </c>
-      <c r="I8">
-        <v>346.42907000000002</v>
-      </c>
-      <c r="J8">
-        <v>8778</v>
-      </c>
-      <c r="K8" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.38903939933431375</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="1"/>
-        <v>0.11212466742683391</v>
-      </c>
-      <c r="M8" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.61683688958319816</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>1488</v>
-      </c>
-      <c r="F9">
-        <v>10567</v>
-      </c>
-      <c r="G9">
-        <v>161.85106200000001</v>
-      </c>
-      <c r="H9">
-        <v>13433</v>
-      </c>
-      <c r="I9">
-        <v>306.45082100000002</v>
-      </c>
-      <c r="J9">
-        <v>7464</v>
-      </c>
-      <c r="K9" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.21335517010347649</v>
-      </c>
-      <c r="L9" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.29365004258540739</v>
-      </c>
-      <c r="M9" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.47185306447588204</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10">
-        <v>12</v>
-      </c>
-      <c r="E10">
-        <v>2109</v>
-      </c>
-      <c r="F10">
-        <v>4962</v>
-      </c>
-      <c r="G10">
-        <v>85.607489999999999</v>
-      </c>
-      <c r="H10">
-        <v>14909</v>
-      </c>
-      <c r="I10">
-        <v>560.85743500000001</v>
-      </c>
-      <c r="J10">
-        <v>4532</v>
-      </c>
-      <c r="K10" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.6671808974444966</v>
-      </c>
-      <c r="L10" s="2">
-        <f t="shared" si="1"/>
-        <v>-8.6658605401047972E-2</v>
-      </c>
-      <c r="M10" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.84736318954209811</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="E37">
+        <v>6501</v>
+      </c>
+      <c r="F37">
+        <v>10935</v>
+      </c>
+      <c r="G37" s="4">
+        <v>-40.549999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11">
-        <v>14</v>
-      </c>
-      <c r="E11">
-        <v>1000</v>
-      </c>
-      <c r="F11">
-        <v>5320</v>
-      </c>
-      <c r="G11">
-        <v>49.378607000000002</v>
-      </c>
-      <c r="H11">
-        <v>8675</v>
-      </c>
-      <c r="I11">
-        <v>105.78508100000001</v>
-      </c>
-      <c r="J11">
-        <v>7590</v>
-      </c>
-      <c r="K11" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.3867435158501441</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.42669172932330834</v>
-      </c>
-      <c r="M11" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.53321766610926924</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12">
-        <v>14</v>
-      </c>
-      <c r="E12">
-        <v>1000</v>
-      </c>
-      <c r="F12">
-        <v>4252</v>
-      </c>
-      <c r="G12">
-        <v>36.524329999999999</v>
-      </c>
-      <c r="H12">
-        <v>7967</v>
-      </c>
-      <c r="I12">
-        <v>87.638071999999994</v>
-      </c>
-      <c r="J12">
-        <v>3406</v>
-      </c>
-      <c r="K12" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.46629848123509476</v>
-      </c>
-      <c r="L12" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.19896519285042336</v>
-      </c>
-      <c r="M12" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.58323672387498438</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>12</v>
-      </c>
-      <c r="E13">
-        <v>1085</v>
-      </c>
-      <c r="F13">
-        <v>3222</v>
-      </c>
-      <c r="G13">
-        <v>23.810727</v>
-      </c>
-      <c r="H13">
-        <v>8077</v>
-      </c>
-      <c r="I13">
-        <v>90.031066999999993</v>
-      </c>
-      <c r="J13">
-        <v>2767</v>
-      </c>
-      <c r="K13" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.60108951343320538</v>
-      </c>
-      <c r="L13" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.1412166356300435</v>
-      </c>
-      <c r="M13" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.73552765957999799</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14">
-        <v>8</v>
-      </c>
-      <c r="E14">
-        <v>84</v>
-      </c>
-      <c r="F14">
-        <v>289</v>
-      </c>
-      <c r="G14">
-        <v>0.19081300000000001</v>
-      </c>
-      <c r="H14">
-        <v>443</v>
-      </c>
-      <c r="I14">
-        <v>0.279721</v>
-      </c>
-      <c r="J14">
-        <v>266</v>
-      </c>
-      <c r="K14" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.34762979683972917</v>
-      </c>
-      <c r="L14" s="2">
-        <f t="shared" si="1"/>
-        <v>-7.9584775086505188E-2</v>
-      </c>
-      <c r="M14" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.31784528154839997</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>12</v>
-      </c>
-      <c r="F15">
+      <c r="D38">
+        <v>3240</v>
+      </c>
+      <c r="E38">
+        <v>12979</v>
+      </c>
+      <c r="F38">
+        <v>11586</v>
+      </c>
+      <c r="G38" s="4">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="6">
         <v>22</v>
       </c>
-      <c r="G15">
-        <v>1.486E-2</v>
-      </c>
-      <c r="H15">
-        <v>35</v>
-      </c>
-      <c r="I15">
-        <v>5.5510000000000004E-3</v>
-      </c>
-      <c r="J15">
-        <v>24</v>
-      </c>
-      <c r="K15" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.37142857142857144</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="1"/>
-        <v>9.0909090909090828E-2</v>
-      </c>
-      <c r="M15" s="5">
-        <f t="shared" si="2"/>
-        <v>1.6769951360115294</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>84</v>
-      </c>
-      <c r="F16">
-        <v>327</v>
-      </c>
-      <c r="G16">
-        <v>0.27967599999999998</v>
-      </c>
-      <c r="H16">
-        <v>414</v>
-      </c>
-      <c r="I16">
-        <v>0.30827500000000002</v>
-      </c>
-      <c r="J16">
-        <v>247</v>
-      </c>
-      <c r="K16" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.21014492753623193</v>
-      </c>
-      <c r="L16" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.24464831804281351</v>
-      </c>
-      <c r="M16" s="2">
-        <f t="shared" si="2"/>
-        <v>-9.2771064796042579E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <v>12</v>
-      </c>
-      <c r="F17">
-        <v>24</v>
-      </c>
-      <c r="G17">
-        <v>1.1167E-2</v>
-      </c>
-      <c r="H17">
-        <v>38</v>
-      </c>
-      <c r="I17">
-        <v>6.3090000000000004E-3</v>
-      </c>
-      <c r="J17">
-        <v>29</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.36842105263157898</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.20833333333333326</v>
-      </c>
-      <c r="M17" s="5">
-        <f t="shared" si="2"/>
-        <v>0.77001109526073841</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>158</v>
-      </c>
-      <c r="F18">
-        <v>237</v>
-      </c>
-      <c r="G18">
-        <v>0.26958500000000002</v>
-      </c>
-      <c r="H18">
-        <v>433</v>
-      </c>
-      <c r="I18">
-        <v>0.34162100000000001</v>
-      </c>
-      <c r="J18">
-        <v>215</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.45265588914549648</v>
-      </c>
-      <c r="L18" s="2">
-        <f t="shared" si="1"/>
-        <v>-9.2827004219409259E-2</v>
-      </c>
-      <c r="M18" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.210865257112414</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-      <c r="G19">
-        <v>5.1599999999999997E-3</v>
-      </c>
-      <c r="H19">
-        <v>5</v>
-      </c>
-      <c r="I19">
-        <v>2.0890000000000001E-3</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-      <c r="K19" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
-      </c>
-      <c r="M19" s="5">
-        <f t="shared" si="2"/>
-        <v>1.4700813786500713</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20">
-        <v>16</v>
-      </c>
-      <c r="E20">
-        <v>1440</v>
-      </c>
-      <c r="F20">
-        <v>11382</v>
-      </c>
-      <c r="G20">
-        <v>164.80469600000001</v>
-      </c>
-      <c r="H20">
-        <v>13852</v>
-      </c>
-      <c r="I20">
-        <v>378.60474699999997</v>
-      </c>
-      <c r="J20">
-        <v>11815</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.17831360092405424</v>
-      </c>
-      <c r="L20" s="1">
-        <f t="shared" si="1"/>
-        <v>3.8042523282375784E-2</v>
-      </c>
-      <c r="M20" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.56470515146499201</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>160</v>
-      </c>
-      <c r="F21">
-        <v>448</v>
-      </c>
-      <c r="G21">
-        <v>0.668852</v>
-      </c>
-      <c r="H21">
-        <v>878</v>
-      </c>
-      <c r="I21">
-        <v>1.1275869999999999</v>
-      </c>
-      <c r="J21">
-        <v>382</v>
-      </c>
-      <c r="K21" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.48974943052391795</v>
-      </c>
-      <c r="L21" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.1473214285714286</v>
-      </c>
-      <c r="M21" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.40682891874418559</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22">
-        <v>16</v>
-      </c>
-      <c r="E22">
-        <v>1440</v>
-      </c>
-      <c r="F22">
-        <v>11626</v>
-      </c>
-      <c r="G22">
-        <v>165.386697</v>
-      </c>
-      <c r="H22">
-        <v>11727</v>
-      </c>
-      <c r="I22">
-        <v>309.21366599999999</v>
-      </c>
-      <c r="J22">
-        <v>6468</v>
-      </c>
-      <c r="K22" s="2">
-        <f t="shared" si="0"/>
-        <v>-8.6126033938773716E-3</v>
-      </c>
-      <c r="L22" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.44366076036469981</v>
-      </c>
-      <c r="M22" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.46513781509255803</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23">
-        <v>8</v>
-      </c>
-      <c r="E23">
-        <v>160</v>
-      </c>
-      <c r="F23">
-        <v>507</v>
-      </c>
-      <c r="G23">
-        <v>0.79593100000000006</v>
-      </c>
-      <c r="H23">
-        <v>883</v>
-      </c>
-      <c r="I23">
-        <v>1.149607</v>
-      </c>
-      <c r="J23">
-        <v>421</v>
-      </c>
-      <c r="K23" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.42582106455266133</v>
-      </c>
-      <c r="L23" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.16962524654832345</v>
-      </c>
-      <c r="M23" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.30764948369312295</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24">
-        <v>14</v>
-      </c>
-      <c r="E24">
-        <v>2912</v>
-      </c>
-      <c r="F24">
-        <v>15866</v>
-      </c>
-      <c r="G24">
-        <v>318.762201</v>
-      </c>
-      <c r="H24">
-        <v>24224</v>
-      </c>
-      <c r="I24">
-        <v>1493.9029410000001</v>
-      </c>
-      <c r="J24">
-        <v>8374</v>
-      </c>
-      <c r="K24" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.34502972258916775</v>
-      </c>
-      <c r="L24" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.47220471448380186</v>
-      </c>
-      <c r="M24" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.78662455755885685</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25">
-        <v>6</v>
-      </c>
-      <c r="E25">
-        <v>164</v>
-      </c>
-      <c r="F25">
-        <v>217</v>
-      </c>
-      <c r="G25">
-        <v>0.58277299999999999</v>
-      </c>
-      <c r="H25">
-        <v>471</v>
-      </c>
-      <c r="I25">
-        <v>0.57758100000000001</v>
-      </c>
-      <c r="J25">
-        <v>191</v>
-      </c>
-      <c r="K25" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.53927813163481952</v>
-      </c>
-      <c r="L25" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.11981566820276501</v>
-      </c>
-      <c r="M25" s="5">
-        <f t="shared" si="2"/>
-        <v>8.9892153654638207E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26">
-        <v>16</v>
-      </c>
-      <c r="E26">
-        <v>2688</v>
-      </c>
-      <c r="F26">
-        <v>20605</v>
-      </c>
-      <c r="G26">
-        <v>626.60672199999999</v>
-      </c>
-      <c r="H26">
-        <v>28018</v>
-      </c>
-      <c r="I26">
-        <v>1932.4593809999999</v>
-      </c>
-      <c r="J26">
-        <v>11809</v>
-      </c>
-      <c r="K26" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.26457991291312732</v>
-      </c>
-      <c r="L26" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.42688667799077895</v>
-      </c>
-      <c r="M26" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.67574649787684204</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
-      </c>
-      <c r="E27">
-        <v>2688</v>
-      </c>
-      <c r="F27">
-        <v>9143</v>
-      </c>
-      <c r="G27">
-        <v>335.78666199999998</v>
-      </c>
-      <c r="H27">
-        <v>29280</v>
-      </c>
-      <c r="I27">
-        <v>2134.8060519999999</v>
-      </c>
-      <c r="J27">
-        <v>10652</v>
-      </c>
-      <c r="K27" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.68773907103825138</v>
-      </c>
-      <c r="L27" s="1">
-        <f t="shared" si="1"/>
-        <v>0.1650442961828722</v>
-      </c>
-      <c r="M27" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.84270858625053213</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28">
-        <v>20</v>
-      </c>
-      <c r="E28">
-        <v>684</v>
-      </c>
-      <c r="F28">
-        <v>4953</v>
-      </c>
-      <c r="G28">
-        <v>34.247933000000003</v>
-      </c>
-      <c r="H28">
-        <v>6308</v>
-      </c>
-      <c r="I28">
-        <v>60.474814000000002</v>
-      </c>
-      <c r="J28">
-        <v>4740</v>
-      </c>
-      <c r="K28" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.21480659480025366</v>
-      </c>
-      <c r="L28" s="2">
-        <f t="shared" si="1"/>
-        <v>-4.300423985463353E-2</v>
-      </c>
-      <c r="M28" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.43368270632465278</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29">
-        <v>20</v>
-      </c>
-      <c r="E29">
-        <v>684</v>
-      </c>
-      <c r="F29">
-        <v>4946</v>
-      </c>
-      <c r="G29">
-        <v>32.466031000000001</v>
-      </c>
-      <c r="H29">
-        <v>5807</v>
-      </c>
-      <c r="I29">
-        <v>55.383809999999997</v>
-      </c>
-      <c r="J29">
-        <v>5704</v>
-      </c>
-      <c r="K29" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.14826933011882215</v>
-      </c>
-      <c r="L29" s="1">
-        <f t="shared" si="1"/>
-        <v>0.15325515568135861</v>
-      </c>
-      <c r="M29" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.41379924927519429</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30">
-        <v>22</v>
-      </c>
-      <c r="E30">
+      <c r="D39" s="6">
         <v>3240</v>
       </c>
-      <c r="F30">
-        <v>42385</v>
-      </c>
-      <c r="G30">
-        <v>1592.0266979999999</v>
-      </c>
-      <c r="H30">
-        <v>35792</v>
-      </c>
-      <c r="I30">
-        <v>3037.7464949999999</v>
-      </c>
-      <c r="J30">
-        <v>47282</v>
-      </c>
-      <c r="K30" s="5">
-        <f t="shared" si="0"/>
-        <v>0.18420317389360741</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" si="1"/>
-        <v>0.11553615665919548</v>
-      </c>
-      <c r="M30" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.47591851373364846</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31">
-        <v>12</v>
-      </c>
-      <c r="E31">
-        <v>640</v>
-      </c>
-      <c r="F31">
-        <v>2564</v>
-      </c>
-      <c r="G31">
-        <v>15.482094999999999</v>
-      </c>
-      <c r="H31">
-        <v>4250</v>
-      </c>
-      <c r="I31">
-        <v>28.972878999999999</v>
-      </c>
-      <c r="J31">
-        <v>3275</v>
-      </c>
-      <c r="K31" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.39670588235294113</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="1"/>
-        <v>0.27730109204368181</v>
-      </c>
-      <c r="M31" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.4656349132580162</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32">
-        <v>22</v>
-      </c>
-      <c r="E32">
-        <v>3240</v>
-      </c>
-      <c r="F32">
-        <v>24416</v>
-      </c>
-      <c r="G32">
-        <v>852.84564499999999</v>
-      </c>
-      <c r="H32">
-        <v>33673</v>
-      </c>
-      <c r="I32">
-        <v>3113.253412</v>
-      </c>
-      <c r="J32">
-        <v>16037</v>
-      </c>
-      <c r="K32" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.27490868054524398</v>
-      </c>
-      <c r="L32" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.34317660550458717</v>
-      </c>
-      <c r="M32" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.7260596770848412</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33">
-        <v>12</v>
-      </c>
-      <c r="E33">
-        <v>640</v>
-      </c>
-      <c r="F33">
-        <v>2503</v>
-      </c>
-      <c r="G33">
-        <v>14.346698</v>
-      </c>
-      <c r="H33">
-        <v>4331</v>
-      </c>
-      <c r="I33">
-        <v>29.301047000000001</v>
-      </c>
-      <c r="J33">
-        <v>2336</v>
-      </c>
-      <c r="K33" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.4220734241514662</v>
-      </c>
-      <c r="L33" s="2">
-        <f t="shared" si="1"/>
-        <v>-6.6719936076707897E-2</v>
-      </c>
-      <c r="M33" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.51036910046251927</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34">
-        <v>10</v>
-      </c>
-      <c r="E34">
-        <v>630</v>
-      </c>
-      <c r="F34">
-        <v>1432</v>
-      </c>
-      <c r="G34">
-        <v>6.5066259999999998</v>
-      </c>
-      <c r="H34">
-        <v>3472</v>
-      </c>
-      <c r="I34">
-        <v>20.047049999999999</v>
-      </c>
-      <c r="J34">
-        <v>1468</v>
-      </c>
-      <c r="K34" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.5875576036866359</v>
-      </c>
-      <c r="L34" s="1">
-        <f t="shared" si="1"/>
-        <v>2.5139664804469275E-2</v>
-      </c>
-      <c r="M34" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.67543224564212689</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35">
-        <v>18</v>
-      </c>
-      <c r="E35">
-        <v>2950</v>
-      </c>
-      <c r="F35">
-        <v>21728</v>
-      </c>
-      <c r="G35">
-        <v>508.06735300000003</v>
-      </c>
-      <c r="H35">
-        <v>35602</v>
-      </c>
-      <c r="I35">
-        <v>2431.2650039999999</v>
-      </c>
-      <c r="J35">
-        <v>15910</v>
-      </c>
-      <c r="K35" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.38969720802202124</v>
-      </c>
-      <c r="L35" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.2677650957290133</v>
-      </c>
-      <c r="M35" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.79102757117627642</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36">
-        <v>16</v>
-      </c>
-      <c r="E36">
-        <v>2340</v>
-      </c>
-      <c r="F36">
-        <v>19534</v>
-      </c>
-      <c r="G36">
-        <v>472.31464199999999</v>
-      </c>
-      <c r="H36">
-        <v>25280</v>
-      </c>
-      <c r="I36">
-        <v>1281.476625</v>
-      </c>
-      <c r="J36">
-        <v>13035</v>
-      </c>
-      <c r="K36" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.2272943037974684</v>
-      </c>
-      <c r="L36" s="2">
-        <f t="shared" si="1"/>
-        <v>-0.33270195556465654</v>
-      </c>
-      <c r="M36" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.63142937390683973</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37">
-        <v>16</v>
-      </c>
-      <c r="E37">
-        <v>2340</v>
-      </c>
-      <c r="F37">
-        <v>9597</v>
-      </c>
-      <c r="G37">
-        <v>222.20063200000001</v>
-      </c>
-      <c r="H37">
-        <v>23182</v>
-      </c>
-      <c r="I37">
-        <v>1149.347585</v>
-      </c>
-      <c r="J37">
-        <v>9670</v>
-      </c>
-      <c r="K37" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.58601501164696745</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="1"/>
-        <v>7.6065437115764301E-3</v>
-      </c>
-      <c r="M37" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.8066723810099623</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38">
-        <v>12</v>
-      </c>
-      <c r="E38">
-        <v>640</v>
-      </c>
-      <c r="F38">
-        <v>2200</v>
-      </c>
-      <c r="G38">
-        <v>10.826136999999999</v>
-      </c>
-      <c r="H38">
-        <v>4788</v>
-      </c>
-      <c r="I38">
-        <v>27.872985</v>
-      </c>
-      <c r="J38">
-        <v>2461</v>
-      </c>
-      <c r="K38" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.54051796157059318</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="1"/>
-        <v>0.11863636363636365</v>
-      </c>
-      <c r="M38" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.61159032661912605</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39">
-        <v>12</v>
-      </c>
-      <c r="E39">
-        <v>640</v>
-      </c>
-      <c r="F39">
-        <v>2301</v>
-      </c>
-      <c r="G39">
-        <v>14.329871000000001</v>
-      </c>
-      <c r="H39">
-        <v>4884</v>
-      </c>
-      <c r="I39">
-        <v>32.869433999999998</v>
-      </c>
-      <c r="J39">
-        <v>2415</v>
-      </c>
-      <c r="K39" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.52886977886977893</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" si="1"/>
-        <v>4.9543676662320735E-2</v>
-      </c>
-      <c r="M39" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.56403657574389632</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40">
-        <v>10</v>
-      </c>
-      <c r="E40">
-        <v>630</v>
-      </c>
-      <c r="F40">
-        <v>1432</v>
-      </c>
-      <c r="G40">
-        <v>6.5269760000000003</v>
-      </c>
-      <c r="H40">
-        <v>3472</v>
-      </c>
-      <c r="I40">
-        <v>19.445034</v>
-      </c>
-      <c r="J40">
-        <v>1468</v>
-      </c>
-      <c r="K40" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.5875576036866359</v>
-      </c>
-      <c r="L40" s="1">
-        <f t="shared" si="1"/>
-        <v>2.5139664804469275E-2</v>
-      </c>
-      <c r="M40" s="2">
-        <f t="shared" si="2"/>
-        <v>-0.66433712586977212</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K41" s="2"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K42" s="2"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K43" s="2"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="2"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K44" s="2"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K45" s="2"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="2"/>
+      <c r="E39" s="6">
+        <v>7850</v>
+      </c>
+      <c r="F39" s="6">
+        <v>11058</v>
+      </c>
+      <c r="G39" s="7">
+        <v>-29.01</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G39">
+    <sortCondition ref="D1:D39"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -30921,22 +31528,22 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -33146,6 +33753,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -33184,19 +33792,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -35416,6 +36024,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -35454,19 +36063,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -37686,6 +38295,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -37724,19 +38334,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -39715,6 +40325,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -39753,19 +40364,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -41744,6 +42355,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -41782,19 +42394,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -43695,6 +44307,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -43733,19 +44346,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -45658,6 +46271,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -45696,19 +46310,19 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -47438,6 +48052,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>